--- a/Units.xlsx
+++ b/Units.xlsx
@@ -384,13 +384,13 @@
     <t>Slippery, Vulnerable:Lightning, Resistant:Fire</t>
   </si>
   <si>
-    <t>Dripping, Vulnerable:Fire</t>
-  </si>
-  <si>
     <t>Vulnerable:Fire, Is actually 3 goblins</t>
   </si>
   <si>
     <t>Vulnerable:Fire</t>
+  </si>
+  <si>
+    <t>Dripping, Vulnerable:Fire, Resistant: Frost</t>
   </si>
 </sst>
 </file>
@@ -531,7 +531,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -578,22 +578,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
@@ -605,10 +593,37 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -916,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB128"/>
+  <dimension ref="A1:AB103"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.85546875" style="1"/>
@@ -1068,8 +1083,8 @@
       <c r="C6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="15">
-        <v>4</v>
+      <c r="D6" s="16">
+        <v>3</v>
       </c>
       <c r="E6" s="15">
         <v>2</v>
@@ -1145,39 +1160,39 @@
       <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="18"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="21" t="s">
+      <c r="V7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
@@ -1187,39 +1202,39 @@
       <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="18"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="21" t="s">
+      <c r="V8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="26"/>
     </row>
     <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1315,8 +1330,8 @@
       <c r="G11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>8</v>
+      <c r="H11" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>8</v>
@@ -1377,105 +1392,105 @@
       <c r="C12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="V12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M13" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="21" t="s">
+      <c r="V13" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="O14"/>
       <c r="X14"/>
     </row>
     <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="15" t="s">
+      <c r="D15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="15" t="s">
+      <c r="G15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="6" t="s">
@@ -1528,29 +1543,29 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>1</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="15" t="s">
+      <c r="C16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="7">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>30</v>
+      <c r="H16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="7">
+        <v>45</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>33</v>
@@ -1602,107 +1617,107 @@
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>48</v>
+      <c r="D17" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="17"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="20" t="s">
+      <c r="M17" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="21" t="s">
+      <c r="V17" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="26"/>
+      <c r="AA17" s="26"/>
+      <c r="AB17" s="26"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>122</v>
+      <c r="D18" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="17"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="21" t="s">
+      <c r="V18" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-    </row>
-    <row r="19" spans="3:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W18" s="26"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="15" t="s">
+      <c r="D20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="15" t="s">
+      <c r="G20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L20" s="6" t="s">
@@ -1731,29 +1746,29 @@
       </c>
     </row>
     <row r="21" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C21" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="15">
-        <v>4</v>
-      </c>
-      <c r="E21" s="15">
-        <v>2</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="15">
-        <v>50</v>
+      <c r="C21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="7">
+        <v>3</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="7">
+        <v>40</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>36</v>
@@ -1781,80 +1796,80 @@
       </c>
     </row>
     <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>53</v>
+      <c r="D22" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="17"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="20" t="s">
+      <c r="M22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>123</v>
+      <c r="D23" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="17"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
+      <c r="M23" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
     </row>
     <row r="25" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" s="15" t="s">
+      <c r="D25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H25" s="15" t="s">
+      <c r="G25" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L25" s="6" t="s">
@@ -1882,30 +1897,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C26" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="15">
-        <v>2</v>
-      </c>
-      <c r="E26" s="15">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="15" t="s">
+    <row r="26" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="C26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="7">
+        <v>4</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="15">
-        <v>30</v>
+      <c r="H26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="7">
+        <v>35</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>49</v>
@@ -1933,458 +1948,818 @@
       </c>
     </row>
     <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>55</v>
+      <c r="D27" s="17" t="s">
+        <v>71</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
-      <c r="J27" s="18"/>
+      <c r="J27" s="17"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="20" t="s">
+      <c r="M27" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>100</v>
+      <c r="D28" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
+      <c r="J28" s="17"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="M28" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C30" s="15" t="s">
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+    </row>
+    <row r="30" spans="3:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="C30" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="15" t="s">
+      <c r="D30" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="G30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="L30" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P30" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R30" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S30" s="27" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="31" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="8">
+        <v>3</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="8">
+        <v>30</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="M31" s="27">
+        <v>3</v>
+      </c>
+      <c r="N31" s="27">
+        <v>1</v>
+      </c>
+      <c r="O31" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="P31" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q31" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R31" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S31" s="27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+      <c r="L32" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M32" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="30"/>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+      <c r="L33" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="30"/>
+    </row>
+    <row r="35" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C35" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M35" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O35" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P35" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="8">
+        <v>3</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="8">
+        <v>40</v>
+      </c>
+      <c r="L36" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="27">
+        <v>3</v>
+      </c>
+      <c r="N36" s="27">
+        <v>2</v>
+      </c>
+      <c r="O36" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R36" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="S36" s="27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="20"/>
+      <c r="L37" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M37" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="30"/>
+    </row>
+    <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
+      <c r="L38" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="30"/>
+    </row>
+    <row r="40" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C40" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M40" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N40" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O40" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P40" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R40" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S40" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C41" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="8">
+        <v>3</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="8">
+        <v>45</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="27">
+        <v>2</v>
+      </c>
+      <c r="N41" s="27">
+        <v>1</v>
+      </c>
+      <c r="O41" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q41" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S41" s="27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="L42" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M42" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="30"/>
+    </row>
+    <row r="43" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="L43" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="30"/>
+    </row>
+    <row r="45" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C45" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M45" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O45" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C46" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="8">
+        <v>1</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="8">
+        <v>30</v>
+      </c>
+      <c r="L46" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="15">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>1</v>
-      </c>
-      <c r="F31" s="15" t="s">
+      <c r="M46" s="27">
+        <v>3</v>
+      </c>
+      <c r="N46" s="27">
+        <v>1</v>
+      </c>
+      <c r="O46" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="P46" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="Q46" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="R46" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S46" s="27">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="15" t="s">
+    <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D47" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="L47" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="15" t="s">
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="30"/>
+    </row>
+    <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D48" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="L48" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="15" t="s">
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="30"/>
+    </row>
+    <row r="50" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C50" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="15" t="s">
+      <c r="D50" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="15" t="s">
+      <c r="G50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I50" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J50" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="15" t="s">
+      <c r="L50" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="M50" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N50" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="O50" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="P50" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="R50" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="S50" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="8">
+        <v>2</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J51" s="8">
+        <v>20</v>
+      </c>
+      <c r="L51" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="15">
-        <v>2</v>
-      </c>
-      <c r="E36" s="15">
-        <v>1</v>
-      </c>
-      <c r="F36" s="15" t="s">
+      <c r="M51" s="27">
+        <v>2</v>
+      </c>
+      <c r="N51" s="27">
+        <v>1</v>
+      </c>
+      <c r="O51" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="P51" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="15">
+      <c r="Q51" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="R51" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="S51" s="27">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="15" t="s">
+    <row r="52" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D52" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="L52" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M52" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="15" t="s">
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+    </row>
+    <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D53" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="L53" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M53" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C40" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C41" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="7">
-        <v>3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J41" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-    </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C45" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C46" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="7">
-        <v>3</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-    </row>
-    <row r="48" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D51" s="7">
-        <v>4</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J51" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-    </row>
-    <row r="53" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+      <c r="R53" s="31"/>
+      <c r="S53" s="31"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C55" s="8" t="s">
         <v>0</v>
       </c>
@@ -2410,61 +2785,61 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C56" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D56" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="J56" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="24"/>
-    </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D57" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="24"/>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D58" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
@@ -2490,18 +2865,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C61" s="8" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D61" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" s="8">
         <v>1</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>7</v>
@@ -2510,39 +2885,39 @@
         <v>8</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J61" s="8">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="23"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="24"/>
-    </row>
-    <row r="63" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D62" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+    </row>
+    <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="24"/>
+      <c r="D63" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C65" s="8" t="s">
@@ -2572,16 +2947,16 @@
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D66" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8">
         <v>1</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>7</v>
@@ -2593,36 +2968,36 @@
         <v>8</v>
       </c>
       <c r="J66" s="8">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="19" t="s">
-        <v>77</v>
+      <c r="D67" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
+      <c r="J67" s="20"/>
     </row>
     <row r="68" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="19" t="s">
-        <v>78</v>
+      <c r="D68" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
+      <c r="J68" s="20"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C70" s="8" t="s">
@@ -2652,10 +3027,10 @@
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C71" s="8" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D71" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E71" s="8">
         <v>1</v>
@@ -2664,45 +3039,45 @@
         <v>13</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="H71" s="8">
+        <v>0</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J71" s="8">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
+      <c r="D72" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
     </row>
     <row r="73" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
+      <c r="D73" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C75" s="8" t="s">
@@ -2730,59 +3105,59 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C76" s="8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D76" s="8">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E76" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J76" s="8">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C77" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
+      <c r="D77" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C78" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
+      <c r="D78" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C80" s="8" t="s">
@@ -2812,820 +3187,396 @@
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="8" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D81" s="8">
         <v>1</v>
       </c>
       <c r="E81" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J81" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="19" t="s">
-        <v>110</v>
+      <c r="D82" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
       <c r="G82" s="19"/>
       <c r="H82" s="19"/>
       <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
+      <c r="J82" s="20"/>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C83" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="19" t="s">
-        <v>82</v>
+      <c r="D83" s="18" t="s">
+        <v>102</v>
       </c>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
       <c r="G83" s="19"/>
       <c r="H83" s="19"/>
       <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
+      <c r="J83" s="20"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="8" t="s">
+      <c r="D85" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H85" s="8" t="s">
+      <c r="G85" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I85" s="8" t="s">
+      <c r="I85" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J85" s="8" t="s">
+      <c r="J85" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C86" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C86" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" s="9">
+        <v>5</v>
+      </c>
+      <c r="E86" s="9">
+        <v>2</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C87" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="17"/>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+    </row>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C90" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H90" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E86" s="8">
-        <v>1</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G86" s="8" t="s">
+      <c r="I90" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C91" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="10">
+        <v>3</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I86" s="8" t="s">
+      <c r="H91" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J86" s="8">
+      <c r="I91" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="17"/>
+      <c r="I92" s="17"/>
+      <c r="J92" s="17"/>
+    </row>
+    <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="17"/>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C95" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C96" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" s="10">
+        <v>7</v>
+      </c>
+      <c r="E96" s="10">
+        <v>1</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E97" s="17"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="17"/>
+      <c r="J97" s="17"/>
+    </row>
+    <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E98" s="17"/>
+      <c r="F98" s="17"/>
+      <c r="G98" s="17"/>
+      <c r="H98" s="17"/>
+      <c r="I98" s="17"/>
+      <c r="J98" s="17"/>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C100" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C101" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D101" s="10">
+        <v>2</v>
+      </c>
+      <c r="E101" s="10">
+        <v>1</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="10">
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C87" s="8" t="s">
+    <row r="102" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C102" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C88" s="8" t="s">
+      <c r="D102" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="17"/>
+      <c r="F102" s="17"/>
+      <c r="G102" s="17"/>
+      <c r="H102" s="17"/>
+      <c r="I102" s="17"/>
+      <c r="J102" s="17"/>
+    </row>
+    <row r="103" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C103" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19"/>
-    </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C90" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H90" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C91" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D91" s="8">
-        <v>2</v>
-      </c>
-      <c r="E91" s="8">
-        <v>1</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="8">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D92" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="24"/>
-    </row>
-    <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C93" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="24"/>
-    </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C95" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C96" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="8">
-        <v>8</v>
-      </c>
-      <c r="E96" s="8">
-        <v>1</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H96" s="8">
-        <v>0</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J96" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="97" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C97" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
-    </row>
-    <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C98" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="19"/>
-    </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C100" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="101" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C101" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D101" s="8">
-        <v>12</v>
-      </c>
-      <c r="E101" s="8">
-        <v>3</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C102" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E102" s="19"/>
-      <c r="F102" s="19"/>
-      <c r="G102" s="19"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="19"/>
-      <c r="J102" s="19"/>
-    </row>
-    <row r="103" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C103" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E103" s="19"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19"/>
-    </row>
-    <row r="105" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C105" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I105" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C106" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D106" s="8">
-        <v>1</v>
-      </c>
-      <c r="E106" s="8">
-        <v>2</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J106" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="107" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C107" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D107" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="23"/>
-      <c r="J107" s="24"/>
-    </row>
-    <row r="108" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C108" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D108" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="23"/>
-      <c r="H108" s="23"/>
-      <c r="I108" s="23"/>
-      <c r="J108" s="24"/>
-    </row>
-    <row r="110" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C110" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I110" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J110" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C111" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D111" s="9">
-        <v>5</v>
-      </c>
-      <c r="E111" s="9">
-        <v>2</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I111" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J111" s="9">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="112" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C112" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="19"/>
-      <c r="I112" s="19"/>
-      <c r="J112" s="19"/>
-    </row>
-    <row r="113" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C113" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E113" s="19"/>
-      <c r="F113" s="19"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="19"/>
-      <c r="I113" s="19"/>
-      <c r="J113" s="19"/>
-    </row>
-    <row r="115" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C115" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I115" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J115" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="116" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C116" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D116" s="10">
-        <v>3</v>
-      </c>
-      <c r="E116" s="10">
-        <v>1</v>
-      </c>
-      <c r="F116" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J116" s="10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="117" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C117" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="E117" s="19"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
-      <c r="H117" s="19"/>
-      <c r="I117" s="19"/>
-      <c r="J117" s="19"/>
-    </row>
-    <row r="118" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C118" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19"/>
-      <c r="I118" s="19"/>
-      <c r="J118" s="19"/>
-    </row>
-    <row r="120" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C120" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H120" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="121" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C121" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D121" s="10">
-        <v>7</v>
-      </c>
-      <c r="E121" s="10">
-        <v>1</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I121" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J121" s="10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="122" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C122" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E122" s="19"/>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="19"/>
-      <c r="I122" s="19"/>
-      <c r="J122" s="19"/>
-    </row>
-    <row r="123" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C123" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E123" s="19"/>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
-      <c r="H123" s="19"/>
-      <c r="I123" s="19"/>
-      <c r="J123" s="19"/>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C125" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I125" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J125" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="126" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C126" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D126" s="10">
-        <v>2</v>
-      </c>
-      <c r="E126" s="10">
-        <v>1</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H126" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I126" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J126" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="127" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C127" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
-      <c r="I127" s="19"/>
-      <c r="J127" s="19"/>
-    </row>
-    <row r="128" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C128" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D128" s="19" t="s">
+      <c r="D103" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
-      <c r="I128" s="19"/>
-      <c r="J128" s="19"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
+      <c r="J103" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D117:J117"/>
-    <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D122:J122"/>
-    <mergeCell ref="D123:J123"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="D108:J108"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="M38:S38"/>
     <mergeCell ref="D87:J87"/>
     <mergeCell ref="D88:J88"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="M23:S23"/>
     <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -3637,22 +3588,46 @@
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="D13:J13"/>
+    <mergeCell ref="M27:S27"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D22:J22"/>
     <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="V17:AB17"/>
-    <mergeCell ref="V18:AB18"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
     <mergeCell ref="D57:J57"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -291,9 +291,6 @@
     <t>Hammerfall bunker</t>
   </si>
   <si>
-    <t>Resistant:Physical, Immovable</t>
-  </si>
-  <si>
     <t>The Great Awful Mass</t>
   </si>
   <si>
@@ -312,12 +309,6 @@
     <t>Grape reaper</t>
   </si>
   <si>
-    <t>Old great Unclean one</t>
-  </si>
-  <si>
-    <t>Slimey, Resistance:Poison, Putrid</t>
-  </si>
-  <si>
     <t>Reflecting, Fragile</t>
   </si>
   <si>
@@ -369,9 +360,6 @@
     <t>Decaying</t>
   </si>
   <si>
-    <t>A game of skeletons</t>
-  </si>
-  <si>
     <t>Old ugly skeletons</t>
   </si>
   <si>
@@ -391,6 +379,54 @@
   </si>
   <si>
     <t>Dripping, Vulnerable:Fire, Resistant: Frost</t>
+  </si>
+  <si>
+    <t>A game of skeletons, Decaying, Fragile</t>
+  </si>
+  <si>
+    <t>Protected, Reflecting</t>
+  </si>
+  <si>
+    <t>Bone construct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dota bristleback made of bones </t>
+  </si>
+  <si>
+    <t>Roach mage</t>
+  </si>
+  <si>
+    <t>Cowardly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the old ugly citadel beastmen </t>
+  </si>
+  <si>
+    <t>Gas construct</t>
+  </si>
+  <si>
+    <t>Djin looking yellow cloud</t>
+  </si>
+  <si>
+    <t>Explosive, Resistant:Physical, Vulnerable:Fire</t>
+  </si>
+  <si>
+    <t>Squad of infantrymen</t>
+  </si>
+  <si>
+    <t>Men with spears modeled after Guard 9th codex art</t>
+  </si>
+  <si>
+    <t>Woundable</t>
+  </si>
+  <si>
+    <t>Resistant:Physical, Immovable, Woundable</t>
+  </si>
+  <si>
+    <t>Slimey, Resistant:Poison, Putrid, Woundable</t>
+  </si>
+  <si>
+    <t>Great Unclean one</t>
   </si>
 </sst>
 </file>
@@ -531,7 +567,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -584,6 +620,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -591,24 +636,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
@@ -623,7 +650,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -931,54 +973,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB103"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB123"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
-    <col min="12" max="12" width="20.28515625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="1"/>
-    <col min="17" max="17" width="14.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="20.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="1"/>
+    <col min="15" max="15" width="10.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-    </row>
-    <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+    </row>
+    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -989,7 +1031,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1076,7 +1118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>15</v>
       </c>
@@ -1153,48 +1195,48 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="21" t="s">
+      <c r="M7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="26" t="s">
+      <c r="V7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+    </row>
+    <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>16</v>
       </c>
@@ -1202,41 +1244,41 @@
       <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="33"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="26" t="s">
+      <c r="V8" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-    </row>
-    <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
       <c r="X9"/>
     </row>
@@ -1314,7 +1356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="15" t="s">
         <v>42</v>
       </c>
@@ -1388,83 +1430,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="24"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="26" t="s">
+      <c r="V12" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+    </row>
+    <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="24"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="33"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="W13" s="26"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-    </row>
-    <row r="14" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="V13" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O14"/>
       <c r="X14"/>
     </row>
@@ -1616,83 +1658,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="21" t="s">
+      <c r="M17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="26" t="s">
+      <c r="V17" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="30"/>
+    </row>
+    <row r="18" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="21" t="s">
+      <c r="M18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="26" t="s">
+      <c r="V18" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="26"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
-      <c r="AB18" s="26"/>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+    </row>
+    <row r="19" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
@@ -1745,7 +1787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C21" s="7" t="s">
         <v>69</v>
       </c>
@@ -1795,59 +1837,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="21" t="s">
+      <c r="M22" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-    </row>
-    <row r="25" spans="3:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="M23" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+    </row>
+    <row r="25" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C26" s="7" t="s">
         <v>70</v>
       </c>
@@ -1947,59 +1989,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M27" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-    </row>
-    <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+    </row>
+    <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-    </row>
-    <row r="30" spans="3:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="M28" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+    </row>
+    <row r="30" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30" s="8" t="s">
         <v>0</v>
       </c>
@@ -2024,34 +2066,34 @@
       <c r="J30" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L30" s="27" t="s">
+      <c r="L30" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N30" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="O30" s="27" t="s">
+      <c r="M30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P30" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q30" s="27" t="s">
+      <c r="P30" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="R30" s="27" t="s">
+      <c r="R30" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="S30" s="27" t="s">
+      <c r="S30" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C31" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D31" s="8">
         <v>3</v>
@@ -2074,84 +2116,84 @@
       <c r="J31" s="8">
         <v>30</v>
       </c>
-      <c r="L31" s="27" t="s">
+      <c r="L31" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="M31" s="27">
-        <v>3</v>
-      </c>
-      <c r="N31" s="27">
-        <v>1</v>
-      </c>
-      <c r="O31" s="27" t="s">
+      <c r="M31" s="18">
+        <v>3</v>
+      </c>
+      <c r="N31" s="18">
+        <v>1</v>
+      </c>
+      <c r="O31" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="P31" s="27" t="s">
+      <c r="P31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Q31" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="R31" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="S31" s="27">
+      <c r="Q31" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R31" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="S31" s="18">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="20"/>
-      <c r="L32" s="27" t="s">
+      <c r="D32" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="23"/>
+      <c r="L32" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="28" t="s">
+      <c r="M32" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="30"/>
-    </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="27"/>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="20"/>
-      <c r="L33" s="27" t="s">
+      <c r="D33" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="23"/>
+      <c r="L33" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="30"/>
-    </row>
-    <row r="35" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="M33" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="27"/>
+    </row>
+    <row r="35" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
         <v>0</v>
       </c>
@@ -2176,32 +2218,32 @@
       <c r="J35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L35" s="27" t="s">
+      <c r="L35" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N35" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="O35" s="27" t="s">
+      <c r="M35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O35" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P35" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="27" t="s">
+      <c r="P35" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="R35" s="27" t="s">
+      <c r="R35" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="S35" s="27" t="s">
+      <c r="S35" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C36" s="8" t="s">
         <v>73</v>
       </c>
@@ -2226,84 +2268,84 @@
       <c r="J36" s="8">
         <v>40</v>
       </c>
-      <c r="L36" s="27" t="s">
+      <c r="L36" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="M36" s="27">
-        <v>3</v>
-      </c>
-      <c r="N36" s="27">
-        <v>2</v>
-      </c>
-      <c r="O36" s="27" t="s">
+      <c r="M36" s="18">
+        <v>3</v>
+      </c>
+      <c r="N36" s="18">
+        <v>2</v>
+      </c>
+      <c r="O36" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="P36" s="27" t="s">
+      <c r="P36" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="Q36" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="R36" s="27" t="s">
+      <c r="Q36" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R36" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S36" s="27">
+      <c r="S36" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="20"/>
-      <c r="L37" s="27" t="s">
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="23"/>
+      <c r="L37" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="28" t="s">
+      <c r="M37" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="30"/>
-    </row>
-    <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="27"/>
+    </row>
+    <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="20"/>
-      <c r="L38" s="27" t="s">
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="23"/>
+      <c r="L38" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="30"/>
-    </row>
-    <row r="40" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="M38" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="27"/>
+    </row>
+    <row r="40" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C40" s="8" t="s">
         <v>0</v>
       </c>
@@ -2328,32 +2370,32 @@
       <c r="J40" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="27" t="s">
+      <c r="L40" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N40" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="O40" s="27" t="s">
+      <c r="M40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N40" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O40" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P40" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="27" t="s">
+      <c r="P40" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="R40" s="27" t="s">
+      <c r="R40" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="S40" s="27" t="s">
+      <c r="S40" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C41" s="8" t="s">
         <v>76</v>
       </c>
@@ -2378,84 +2420,84 @@
       <c r="J41" s="8">
         <v>45</v>
       </c>
-      <c r="L41" s="27" t="s">
+      <c r="L41" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="M41" s="27">
-        <v>2</v>
-      </c>
-      <c r="N41" s="27">
-        <v>1</v>
-      </c>
-      <c r="O41" s="27" t="s">
+      <c r="M41" s="18">
+        <v>2</v>
+      </c>
+      <c r="N41" s="18">
+        <v>1</v>
+      </c>
+      <c r="O41" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="P41" s="27" t="s">
+      <c r="P41" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Q41" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="R41" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="S41" s="27">
+      <c r="Q41" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="S41" s="18">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="L42" s="27" t="s">
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="L42" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="28" t="s">
+      <c r="M42" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="30"/>
-    </row>
-    <row r="43" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="27"/>
+    </row>
+    <row r="43" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C43" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="L43" s="27" t="s">
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="L43" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="30"/>
-    </row>
-    <row r="45" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="M43" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="27"/>
+    </row>
+    <row r="45" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="8" t="s">
         <v>0</v>
       </c>
@@ -2480,32 +2522,32 @@
       <c r="J45" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L45" s="27" t="s">
+      <c r="L45" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N45" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="O45" s="27" t="s">
+      <c r="M45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O45" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P45" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="27" t="s">
+      <c r="P45" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="R45" s="27" t="s">
+      <c r="R45" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="S45" s="27" t="s">
+      <c r="S45" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C46" s="8" t="s">
         <v>79</v>
       </c>
@@ -2530,84 +2572,84 @@
       <c r="J46" s="8">
         <v>30</v>
       </c>
-      <c r="L46" s="27" t="s">
+      <c r="L46" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M46" s="27">
-        <v>3</v>
-      </c>
-      <c r="N46" s="27">
-        <v>1</v>
-      </c>
-      <c r="O46" s="27" t="s">
+      <c r="M46" s="18">
+        <v>3</v>
+      </c>
+      <c r="N46" s="18">
+        <v>1</v>
+      </c>
+      <c r="O46" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="P46" s="27" t="s">
+      <c r="P46" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Q46" s="27" t="s">
+      <c r="Q46" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="R46" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="S46" s="27">
+      <c r="R46" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="S46" s="18">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="L47" s="27" t="s">
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="L47" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="28" t="s">
+      <c r="M47" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="30"/>
-    </row>
-    <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="26"/>
+      <c r="S47" s="27"/>
+    </row>
+    <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="L48" s="27" t="s">
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="L48" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="28" t="s">
+      <c r="M48" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="30"/>
-    </row>
-    <row r="50" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="27"/>
+    </row>
+    <row r="50" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="8" t="s">
         <v>0</v>
       </c>
@@ -2632,34 +2674,34 @@
       <c r="J50" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L50" s="27" t="s">
+      <c r="L50" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N50" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="O50" s="27" t="s">
+      <c r="M50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N50" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O50" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P50" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q50" s="27" t="s">
+      <c r="P50" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="R50" s="27" t="s">
+      <c r="R50" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="S50" s="27" t="s">
+      <c r="S50" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C51" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D51" s="8">
         <v>2</v>
@@ -2682,84 +2724,84 @@
       <c r="J51" s="8">
         <v>20</v>
       </c>
-      <c r="L51" s="27" t="s">
+      <c r="L51" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="M51" s="27">
-        <v>2</v>
-      </c>
-      <c r="N51" s="27">
-        <v>1</v>
-      </c>
-      <c r="O51" s="27" t="s">
+      <c r="M51" s="18">
+        <v>2</v>
+      </c>
+      <c r="N51" s="18">
+        <v>1</v>
+      </c>
+      <c r="O51" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="P51" s="27" t="s">
+      <c r="P51" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Q51" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="R51" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="S51" s="27">
+      <c r="Q51" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R51" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="S51" s="18">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="L52" s="27" t="s">
+      <c r="D52" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="L52" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="31" t="s">
+      <c r="M52" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="31"/>
-    </row>
-    <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="24"/>
+    </row>
+    <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="L53" s="27" t="s">
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="L53" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="M53" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="N53" s="24"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24"/>
+      <c r="R53" s="24"/>
+      <c r="S53" s="24"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C55" s="8" t="s">
         <v>0</v>
       </c>
@@ -2785,9 +2827,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C56" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D56" s="8">
         <v>1</v>
@@ -2811,35 +2853,35 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="D57" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
@@ -2865,7 +2907,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C61" s="8" t="s">
         <v>83</v>
       </c>
@@ -2891,35 +2933,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-    </row>
-    <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-    </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C65" s="8" t="s">
         <v>0</v>
       </c>
@@ -2945,7 +2987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C66" s="8" t="s">
         <v>86</v>
       </c>
@@ -2971,35 +3013,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
-    </row>
-    <row r="68" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="23"/>
+    </row>
+    <row r="68" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="20"/>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="23"/>
+    </row>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="8" t="s">
         <v>0</v>
       </c>
@@ -3025,7 +3067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C71" s="8" t="s">
         <v>89</v>
       </c>
@@ -3051,35 +3093,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-    </row>
-    <row r="73" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-    </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D73" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+    </row>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="8" t="s">
         <v>0</v>
       </c>
@@ -3105,9 +3147,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C76" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D76" s="8">
         <v>12</v>
@@ -3119,7 +3161,7 @@
         <v>44</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>8</v>
@@ -3131,35 +3173,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C77" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-    </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D77" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+    </row>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C78" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-    </row>
-    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D78" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C80" s="8" t="s">
         <v>0</v>
       </c>
@@ -3185,9 +3227,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D81" s="8">
         <v>1</v>
@@ -3211,35 +3253,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="20"/>
-    </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D82" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="23"/>
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="20"/>
-    </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D83" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="22"/>
+      <c r="J83" s="23"/>
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="9" t="s">
         <v>0</v>
       </c>
@@ -3265,9 +3307,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D86" s="9">
         <v>5</v>
@@ -3291,35 +3333,35 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C87" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D87" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C88" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-    </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D88" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
+    </row>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C90" s="10" t="s">
         <v>0</v>
       </c>
@@ -3345,9 +3387,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C91" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D91" s="10">
         <v>3</v>
@@ -3371,35 +3413,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E92" s="17"/>
-      <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-      <c r="J92" s="17"/>
-    </row>
-    <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D92" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+    </row>
+    <row r="93" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E93" s="17"/>
-      <c r="F93" s="17"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17"/>
-    </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D93" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="10" t="s">
         <v>0</v>
       </c>
@@ -3425,9 +3467,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D96" s="10">
         <v>7</v>
@@ -3451,35 +3493,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-    </row>
-    <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E97" s="20"/>
+      <c r="F97" s="20"/>
+      <c r="G97" s="20"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="20"/>
+      <c r="J97" s="20"/>
+    </row>
+    <row r="98" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E98" s="17"/>
-      <c r="F98" s="17"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
-      <c r="J98" s="17"/>
-    </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D98" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" s="20"/>
+      <c r="F98" s="20"/>
+      <c r="G98" s="20"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="20"/>
+      <c r="J98" s="20"/>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="10" t="s">
         <v>0</v>
       </c>
@@ -3505,9 +3547,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C101" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D101" s="10">
         <v>2</v>
@@ -3528,40 +3570,359 @@
         <v>8</v>
       </c>
       <c r="J101" s="10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102" spans="3:10" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="102" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C102" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E102" s="17"/>
-      <c r="F102" s="17"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="17"/>
-      <c r="J102" s="17"/>
-    </row>
-    <row r="103" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D102" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="20"/>
+      <c r="J102" s="20"/>
+    </row>
+    <row r="103" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C103" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E103" s="17"/>
-      <c r="F103" s="17"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="17"/>
-      <c r="I103" s="17"/>
-      <c r="J103" s="17"/>
+      <c r="D103" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="20"/>
+      <c r="J103" s="20"/>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C105" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F105" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H105" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I105" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J105" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C106" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D106" s="17">
+        <v>3</v>
+      </c>
+      <c r="E106" s="17">
+        <v>1</v>
+      </c>
+      <c r="F106" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H106" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J106" s="17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C107" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="20"/>
+      <c r="I107" s="20"/>
+      <c r="J107" s="20"/>
+    </row>
+    <row r="108" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C108" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="20"/>
+      <c r="J108" s="20"/>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C110" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D110" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F110" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H110" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I110" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J110" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C111" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D111" s="17">
+        <v>3</v>
+      </c>
+      <c r="E111" s="17">
+        <v>1</v>
+      </c>
+      <c r="F111" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G111" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H111" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I111" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J111" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C112" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
+      <c r="I112" s="20"/>
+      <c r="J112" s="20"/>
+    </row>
+    <row r="113" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C113" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="20"/>
+      <c r="J113" s="20"/>
+    </row>
+    <row r="115" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C115" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H115" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I115" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J115" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C116" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116" s="17">
+        <v>2</v>
+      </c>
+      <c r="E116" s="17">
+        <v>1</v>
+      </c>
+      <c r="F116" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J116" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C117" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" s="20"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="20"/>
+      <c r="I117" s="20"/>
+      <c r="J117" s="20"/>
+    </row>
+    <row r="118" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C118" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
+      <c r="I118" s="20"/>
+      <c r="J118" s="20"/>
+    </row>
+    <row r="120" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C120" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F120" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H120" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I120" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J120" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C121" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D121" s="17">
+        <v>12</v>
+      </c>
+      <c r="E121" s="17">
+        <v>2</v>
+      </c>
+      <c r="F121" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H121" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I121" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C122" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="E122" s="20"/>
+      <c r="F122" s="20"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="20"/>
+      <c r="J122" s="20"/>
+    </row>
+    <row r="123" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C123" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E123" s="20"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="20"/>
+      <c r="I123" s="20"/>
+      <c r="J123" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="M38:S38"/>
+  <mergeCells count="75">
     <mergeCell ref="D87:J87"/>
     <mergeCell ref="D88:J88"/>
     <mergeCell ref="M22:S22"/>
@@ -3593,12 +3954,8 @@
     <mergeCell ref="D33:J33"/>
     <mergeCell ref="D37:J37"/>
     <mergeCell ref="D38:J38"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
     <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M38:S38"/>
     <mergeCell ref="M53:S53"/>
     <mergeCell ref="D17:J17"/>
     <mergeCell ref="D18:J18"/>
@@ -3610,6 +3967,11 @@
     <mergeCell ref="D48:J48"/>
     <mergeCell ref="D52:J52"/>
     <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
     <mergeCell ref="D57:J57"/>
     <mergeCell ref="D58:J58"/>
     <mergeCell ref="D62:J62"/>
@@ -3628,50 +3990,59 @@
     <mergeCell ref="D97:J97"/>
     <mergeCell ref="D98:J98"/>
     <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D118:J118"/>
+    <mergeCell ref="D122:J122"/>
+    <mergeCell ref="D123:J123"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D113:J113"/>
+    <mergeCell ref="D117:J117"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -3685,7 +4056,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="161">
   <si>
     <t>Name</t>
   </si>
@@ -427,6 +427,78 @@
   </si>
   <si>
     <t>Great Unclean one</t>
+  </si>
+  <si>
+    <t>Polymorphed animal</t>
+  </si>
+  <si>
+    <t>Water mage</t>
+  </si>
+  <si>
+    <t>3, only diagonals</t>
+  </si>
+  <si>
+    <t>Triton or Poseidon</t>
+  </si>
+  <si>
+    <t>Hydrokinesis</t>
+  </si>
+  <si>
+    <t>Crude mage</t>
+  </si>
+  <si>
+    <t>Water hazard but in oiled robes</t>
+  </si>
+  <si>
+    <t>Oliokinesis</t>
+  </si>
+  <si>
+    <t>Storm mage</t>
+  </si>
+  <si>
+    <t>Jacob's animated greek mythology Zeus</t>
+  </si>
+  <si>
+    <t>Stormokinesis</t>
+  </si>
+  <si>
+    <t>A rabbit, sheep or a big sheep depending on the size</t>
+  </si>
+  <si>
+    <t>Four 3 length line perpendicular to player in all directions 1 space away</t>
+  </si>
+  <si>
+    <t>Battering boar</t>
+  </si>
+  <si>
+    <t>Ben 10 cannonbolt with boar elements</t>
+  </si>
+  <si>
+    <t>Charging</t>
+  </si>
+  <si>
+    <t>Ice citadel</t>
+  </si>
+  <si>
+    <t>Miniature icewind citadel</t>
+  </si>
+  <si>
+    <t>Resistant:Frost, Immovable, Woundable, Freezing</t>
+  </si>
+  <si>
+    <t>Galapo</t>
+  </si>
+  <si>
+    <t>Terraspin</t>
+  </si>
+  <si>
+    <t>Pushing</t>
+  </si>
+  <si>
+    <t>Ardmodrillo</t>
+  </si>
+  <si>
+    <t>Armo</t>
   </si>
 </sst>
 </file>
@@ -567,7 +639,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -629,6 +701,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -650,13 +728,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
@@ -973,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB123"/>
+  <dimension ref="A1:AB178"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -995,30 +1073,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1202,39 +1280,39 @@
       <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="35"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="30" t="s">
+      <c r="V7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
     </row>
     <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
@@ -1244,39 +1322,39 @@
       <c r="C8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="35"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="28" t="s">
+      <c r="M8" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="30" t="s">
+      <c r="V8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1434,77 +1512,77 @@
       <c r="C12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="35"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="28" t="s">
+      <c r="M12" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="30" t="s">
+      <c r="V12" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
     </row>
     <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="35"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="30" t="s">
+      <c r="V13" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O14"/>
@@ -1662,77 +1740,77 @@
       <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="28" t="s">
+      <c r="M17" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="30" t="s">
+      <c r="V17" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
     </row>
     <row r="18" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="28" t="s">
+      <c r="M18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="30" t="s">
+      <c r="V18" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
     </row>
     <row r="19" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="O19"/>
@@ -1841,53 +1919,53 @@
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="28" t="s">
+      <c r="M22" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
     </row>
     <row r="25" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="7" t="s">
@@ -1993,53 +2071,53 @@
       <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="28" t="s">
+      <c r="M27" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
     </row>
     <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="M28" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
     </row>
     <row r="30" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30" s="8" t="s">
@@ -2145,53 +2223,53 @@
       <c r="C32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="23"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
       <c r="L32" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="25" t="s">
+      <c r="M32" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="27"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="29"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="23"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="25"/>
       <c r="L33" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="25" t="s">
+      <c r="M33" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="27"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="29"/>
     </row>
     <row r="35" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
@@ -2297,53 +2375,53 @@
       <c r="C37" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="23"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
       <c r="L37" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="25" t="s">
+      <c r="M37" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="27"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="29"/>
     </row>
     <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="23"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="25"/>
       <c r="L38" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="27"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="29"/>
     </row>
     <row r="40" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C40" s="8" t="s">
@@ -2449,53 +2527,53 @@
       <c r="C42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
       <c r="L42" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="25" t="s">
+      <c r="M42" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="27"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="29"/>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C43" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
       <c r="L43" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="25" t="s">
+      <c r="M43" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="27"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="29"/>
     </row>
     <row r="45" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="8" t="s">
@@ -2601,53 +2679,53 @@
       <c r="C47" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
       <c r="L47" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="25" t="s">
+      <c r="M47" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="26"/>
-      <c r="S47" s="27"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="29"/>
     </row>
     <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
       <c r="L48" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="25" t="s">
+      <c r="M48" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="27"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="29"/>
     </row>
     <row r="50" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="8" t="s">
@@ -2753,53 +2831,53 @@
       <c r="C52" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
       <c r="L52" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="24" t="s">
+      <c r="M52" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N52" s="24"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
-      <c r="R52" s="24"/>
-      <c r="S52" s="24"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
+      <c r="Q52" s="26"/>
+      <c r="R52" s="26"/>
+      <c r="S52" s="26"/>
     </row>
     <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
       <c r="L53" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="24" t="s">
+      <c r="M53" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="N53" s="24"/>
-      <c r="O53" s="24"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="24"/>
-      <c r="R53" s="24"/>
-      <c r="S53" s="24"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="26"/>
+      <c r="S53" s="26"/>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C55" s="8" t="s">
@@ -2857,29 +2935,29 @@
       <c r="C57" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C58" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C60" s="8" t="s">
@@ -2937,29 +3015,29 @@
       <c r="C62" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
     </row>
     <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C65" s="8" t="s">
@@ -3017,29 +3095,29 @@
       <c r="C67" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="23"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="25"/>
     </row>
     <row r="68" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="23"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="8" t="s">
@@ -3097,29 +3175,29 @@
       <c r="C72" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="D72" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
     </row>
     <row r="73" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="20" t="s">
+      <c r="D73" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="8" t="s">
@@ -3177,29 +3255,29 @@
       <c r="C77" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="20" t="s">
+      <c r="D77" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="20"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C78" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="20" t="s">
+      <c r="D78" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C80" s="8" t="s">
@@ -3257,29 +3335,29 @@
       <c r="C82" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="22"/>
-      <c r="J82" s="23"/>
+      <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="24"/>
+      <c r="H82" s="24"/>
+      <c r="I82" s="24"/>
+      <c r="J82" s="25"/>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="22"/>
-      <c r="J83" s="23"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="24"/>
+      <c r="J83" s="25"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="9" t="s">
@@ -3337,29 +3415,29 @@
       <c r="C87" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D87" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="20"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="22"/>
+      <c r="J87" s="22"/>
     </row>
     <row r="88" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C88" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="20" t="s">
+      <c r="D88" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
     </row>
     <row r="90" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C90" s="10" t="s">
@@ -3417,29 +3495,29 @@
       <c r="C92" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="20" t="s">
+      <c r="D92" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
-      <c r="J92" s="20"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="22"/>
     </row>
     <row r="93" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="20" t="s">
+      <c r="D93" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
+      <c r="J93" s="22"/>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="10" t="s">
@@ -3497,29 +3575,29 @@
       <c r="C97" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="20" t="s">
+      <c r="D97" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-      <c r="J97" s="20"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
     </row>
     <row r="98" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="20" t="s">
+      <c r="D98" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-      <c r="J98" s="20"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
     </row>
     <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="10" t="s">
@@ -3577,29 +3655,29 @@
       <c r="C102" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="20" t="s">
+      <c r="D102" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-      <c r="J102" s="20"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="22"/>
+      <c r="J102" s="22"/>
     </row>
     <row r="103" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C103" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="20" t="s">
+      <c r="D103" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
-      <c r="J103" s="20"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="22"/>
+      <c r="I103" s="22"/>
+      <c r="J103" s="22"/>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C105" s="17" t="s">
@@ -3657,29 +3735,29 @@
       <c r="C107" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="20" t="s">
+      <c r="D107" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E107" s="20"/>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="20"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="22"/>
     </row>
     <row r="108" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C108" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="20" t="s">
+      <c r="D108" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="E108" s="20"/>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
-      <c r="J108" s="20"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="22"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="22"/>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C110" s="17" t="s">
@@ -3737,29 +3815,29 @@
       <c r="C112" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="20" t="s">
+      <c r="D112" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E112" s="20"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
-      <c r="J112" s="20"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
+      <c r="H112" s="22"/>
+      <c r="I112" s="22"/>
+      <c r="J112" s="22"/>
     </row>
     <row r="113" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C113" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="20" t="s">
+      <c r="D113" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
-      <c r="J113" s="20"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="22"/>
+      <c r="H113" s="22"/>
+      <c r="I113" s="22"/>
+      <c r="J113" s="22"/>
     </row>
     <row r="115" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C115" s="17" t="s">
@@ -3817,29 +3895,29 @@
       <c r="C117" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="20" t="s">
+      <c r="D117" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="E117" s="20"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
-      <c r="J117" s="20"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
+      <c r="J117" s="22"/>
     </row>
     <row r="118" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C118" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="20" t="s">
+      <c r="D118" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
-      <c r="J118" s="20"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22"/>
+      <c r="I118" s="22"/>
+      <c r="J118" s="22"/>
     </row>
     <row r="120" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C120" s="17" t="s">
@@ -3890,39 +3968,980 @@
         <v>8</v>
       </c>
       <c r="J121" s="17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="3:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="3:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="20" t="s">
+      <c r="D122" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
-      <c r="J122" s="20"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
+      <c r="I122" s="22"/>
+      <c r="J122" s="22"/>
     </row>
     <row r="123" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C123" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="20" t="s">
+      <c r="D123" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="20"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="22"/>
+      <c r="J123" s="22"/>
+    </row>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C125" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G125" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H125" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I125" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J125" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C126" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D126" s="20">
+        <v>2</v>
+      </c>
+      <c r="E126" s="20">
+        <v>0</v>
+      </c>
+      <c r="F126" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H126" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I126" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J126" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="3:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C127" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="22"/>
+      <c r="J127" s="22"/>
+    </row>
+    <row r="128" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C128" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
+      <c r="J128" s="22"/>
+    </row>
+    <row r="130" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C130" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F130" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H130" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I130" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J130" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C131" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D131" s="20">
+        <v>3</v>
+      </c>
+      <c r="E131" s="20">
+        <v>1</v>
+      </c>
+      <c r="F131" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G131" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H131" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I131" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="J131" s="20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C132" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+    </row>
+    <row r="133" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C133" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
+      <c r="J133" s="22"/>
+    </row>
+    <row r="134" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="M134"/>
+      <c r="N134"/>
+      <c r="O134"/>
+      <c r="P134"/>
+      <c r="Q134"/>
+    </row>
+    <row r="135" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C135" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F135" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H135" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I135" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J135" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M135"/>
+      <c r="N135"/>
+      <c r="O135"/>
+      <c r="P135"/>
+      <c r="Q135"/>
+    </row>
+    <row r="136" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C136" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D136" s="20">
+        <v>3</v>
+      </c>
+      <c r="E136" s="20">
+        <v>1</v>
+      </c>
+      <c r="F136" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I136" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J136" s="20">
+        <v>35</v>
+      </c>
+      <c r="M136"/>
+      <c r="N136"/>
+      <c r="O136"/>
+      <c r="P136"/>
+      <c r="Q136"/>
+    </row>
+    <row r="137" spans="3:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C137" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="22"/>
+      <c r="J137" s="22"/>
+      <c r="M137"/>
+      <c r="N137"/>
+      <c r="O137"/>
+      <c r="P137"/>
+      <c r="Q137"/>
+    </row>
+    <row r="138" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C138" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
+      <c r="M138"/>
+      <c r="N138"/>
+      <c r="O138"/>
+      <c r="P138"/>
+      <c r="Q138"/>
+    </row>
+    <row r="139" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="M139"/>
+      <c r="N139"/>
+      <c r="O139"/>
+      <c r="P139"/>
+      <c r="Q139"/>
+    </row>
+    <row r="140" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D140" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F140" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H140" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I140" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J140" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M140"/>
+      <c r="N140"/>
+      <c r="O140"/>
+      <c r="P140"/>
+      <c r="Q140"/>
+    </row>
+    <row r="141" spans="3:17" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C141" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D141" s="20">
+        <v>4</v>
+      </c>
+      <c r="E141" s="20">
+        <v>1</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I141" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="J141" s="20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142" spans="3:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C142" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E142" s="22"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="22"/>
+      <c r="J142" s="22"/>
+    </row>
+    <row r="143" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E143" s="22"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="22"/>
+      <c r="J143" s="22"/>
+    </row>
+    <row r="145" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C145" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D145" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F145" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G145" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H145" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I145" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J145" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C146" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D146" s="20">
+        <v>4</v>
+      </c>
+      <c r="E146" s="20">
+        <v>1</v>
+      </c>
+      <c r="F146" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H146" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I146" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J146" s="20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C147" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="E147" s="22"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
+      <c r="I147" s="22"/>
+      <c r="J147" s="22"/>
+    </row>
+    <row r="148" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C148" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E148" s="22"/>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22"/>
+      <c r="I148" s="22"/>
+      <c r="J148" s="22"/>
+    </row>
+    <row r="150" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C150" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D150" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E150" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F150" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H150" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I150" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="J150" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C151" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D151" s="20">
+        <v>6</v>
+      </c>
+      <c r="E151" s="20">
+        <v>1</v>
+      </c>
+      <c r="F151" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G151" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H151" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I151" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J151" s="20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C152" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E152" s="22"/>
+      <c r="F152" s="22"/>
+      <c r="G152" s="22"/>
+      <c r="H152" s="22"/>
+      <c r="I152" s="22"/>
+      <c r="J152" s="22"/>
+    </row>
+    <row r="153" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C153" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
+      <c r="H153" s="22"/>
+      <c r="I153" s="22"/>
+      <c r="J153" s="22"/>
+    </row>
+    <row r="155" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C155" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D155" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E155" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F155" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H155" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I155" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J155" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C156" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D156" s="21">
+        <v>3</v>
+      </c>
+      <c r="E156" s="21">
+        <v>1</v>
+      </c>
+      <c r="F156" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I156" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J156" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="157" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C157" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E157" s="22"/>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22"/>
+      <c r="H157" s="22"/>
+      <c r="I157" s="22"/>
+      <c r="J157" s="22"/>
+    </row>
+    <row r="158" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C158" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E158" s="22"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22"/>
+      <c r="H158" s="22"/>
+      <c r="I158" s="22"/>
+      <c r="J158" s="22"/>
+    </row>
+    <row r="160" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C160" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H160" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I160" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J160" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C161" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D161" s="21">
+        <v>3</v>
+      </c>
+      <c r="E161" s="21">
+        <v>1</v>
+      </c>
+      <c r="F161" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H161" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="I161" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J161" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C162" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E162" s="22"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
+      <c r="H162" s="22"/>
+      <c r="I162" s="22"/>
+      <c r="J162" s="22"/>
+    </row>
+    <row r="163" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C163" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E163" s="22"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22"/>
+      <c r="H163" s="22"/>
+      <c r="I163" s="22"/>
+      <c r="J163" s="22"/>
+    </row>
+    <row r="165" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C165" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H165" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I165" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J165" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C166" s="21">
+        <v>3</v>
+      </c>
+      <c r="D166" s="21">
+        <v>3</v>
+      </c>
+      <c r="E166" s="21">
+        <v>1</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I166" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J166" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="167" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C167" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+    </row>
+    <row r="168" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C168" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E168" s="22"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
+      <c r="H168" s="22"/>
+      <c r="I168" s="22"/>
+      <c r="J168" s="22"/>
+    </row>
+    <row r="170" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C170" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D170" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E170" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F170" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H170" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I170" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J170" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C171" s="21">
+        <v>4</v>
+      </c>
+      <c r="D171" s="21">
+        <v>3</v>
+      </c>
+      <c r="E171" s="21">
+        <v>1</v>
+      </c>
+      <c r="F171" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H171" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I171" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J171" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="172" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C172" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E172" s="22"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
+      <c r="H172" s="22"/>
+      <c r="I172" s="22"/>
+      <c r="J172" s="22"/>
+    </row>
+    <row r="173" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C173" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E173" s="22"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
+      <c r="H173" s="22"/>
+      <c r="I173" s="22"/>
+      <c r="J173" s="22"/>
+    </row>
+    <row r="175" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C175" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D175" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E175" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F175" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H175" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I175" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J175" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C176" s="21">
+        <v>5</v>
+      </c>
+      <c r="D176" s="21">
+        <v>3</v>
+      </c>
+      <c r="E176" s="21">
+        <v>1</v>
+      </c>
+      <c r="F176" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H176" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I176" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J176" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C177" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
+      <c r="H177" s="22"/>
+      <c r="I177" s="22"/>
+      <c r="J177" s="22"/>
+    </row>
+    <row r="178" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C178" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E178" s="22"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
+      <c r="H178" s="22"/>
+      <c r="I178" s="22"/>
+      <c r="J178" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="97">
+    <mergeCell ref="D168:J168"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D173:J173"/>
+    <mergeCell ref="D177:J177"/>
+    <mergeCell ref="D178:J178"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D167:J167"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="D137:J137"/>
     <mergeCell ref="D87:J87"/>
     <mergeCell ref="D88:J88"/>
     <mergeCell ref="M22:S22"/>
@@ -3938,6 +4957,7 @@
     <mergeCell ref="D32:J32"/>
     <mergeCell ref="M23:S23"/>
     <mergeCell ref="D27:J27"/>
+    <mergeCell ref="M27:S27"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -3949,7 +4969,6 @@
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="D13:J13"/>
-    <mergeCell ref="M27:S27"/>
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="D33:J33"/>
     <mergeCell ref="D37:J37"/>
@@ -4013,28 +5032,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="29"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="A1" s="30"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="174">
   <si>
     <t>Name</t>
   </si>
@@ -483,9 +483,6 @@
     <t>Terraspin</t>
   </si>
   <si>
-    <t>Pushing</t>
-  </si>
-  <si>
     <t>Ardmodrillo</t>
   </si>
   <si>
@@ -502,6 +499,45 @@
   </si>
   <si>
     <t>Resistant:Physical, Immovable, Woundable, Penetrating</t>
+  </si>
+  <si>
+    <t>Siren</t>
+  </si>
+  <si>
+    <t>Darkest dungeon siren</t>
+  </si>
+  <si>
+    <t>Captivating</t>
+  </si>
+  <si>
+    <t>Pushing, Merging</t>
+  </si>
+  <si>
+    <t>Pushing, Merging, Evading</t>
+  </si>
+  <si>
+    <t>Hazar</t>
+  </si>
+  <si>
+    <t>Hydrokinesis, Merging</t>
+  </si>
+  <si>
+    <t>Boxor</t>
+  </si>
+  <si>
+    <t>Water hazard</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>Merging</t>
+  </si>
+  <si>
+    <t>Watt</t>
+  </si>
+  <si>
+    <t>Evading, Merging</t>
   </si>
 </sst>
 </file>
@@ -642,7 +678,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -707,6 +743,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,6 +761,24 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -731,24 +788,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -1054,54 +1094,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB178"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB183"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
-    <col min="12" max="12" width="20.28515625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="1"/>
-    <col min="17" max="17" width="14.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="20.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="1"/>
+    <col min="15" max="15" width="10.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-    </row>
-    <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+    </row>
+    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1112,7 +1152,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1199,7 +1239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>15</v>
       </c>
@@ -1276,48 +1316,48 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>114</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="23" t="s">
+      <c r="V7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+    </row>
+    <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>16</v>
       </c>
@@ -1325,41 +1365,41 @@
       <c r="C8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="33"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="23" t="s">
+      <c r="V8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-    </row>
-    <row r="9" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
       <c r="X9"/>
     </row>
@@ -1437,7 +1477,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="14" t="s">
         <v>42</v>
       </c>
@@ -1454,7 +1494,7 @@
         <v>7</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>8</v>
@@ -1511,83 +1551,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="33"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="23" t="s">
+      <c r="V12" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+    </row>
+    <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="D13" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="23" t="s">
+      <c r="V13" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-    </row>
-    <row r="14" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O14"/>
       <c r="X14"/>
     </row>
@@ -1739,83 +1779,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="22" t="s">
+      <c r="M17" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="23" t="s">
+      <c r="V17" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+    </row>
+    <row r="18" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="22" t="s">
+      <c r="M18" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="23" t="s">
+      <c r="V18" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+    </row>
+    <row r="19" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="O19"/>
     </row>
     <row r="20" spans="3:28" ht="30" x14ac:dyDescent="0.25">
@@ -1868,7 +1908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C21" s="15" t="s">
         <v>68</v>
       </c>
@@ -1918,59 +1958,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="22" t="s">
+      <c r="M23" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-    </row>
-    <row r="25" spans="3:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+    </row>
+    <row r="25" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="15" t="s">
         <v>0</v>
       </c>
@@ -2020,7 +2060,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C26" s="15" t="s">
         <v>69</v>
       </c>
@@ -2070,59 +2110,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="22" t="s">
+      <c r="M27" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-    </row>
-    <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+    </row>
+    <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="21" t="s">
+      <c r="M28" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-    </row>
-    <row r="30" spans="3:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+    </row>
+    <row r="30" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30" s="15" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +2212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>100</v>
       </c>
@@ -2189,7 +2229,7 @@
         <v>7</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>8</v>
@@ -2222,59 +2262,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
       <c r="L32" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="24" t="s">
+      <c r="M32" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="26"/>
-    </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="27"/>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="33"/>
+      <c r="D33" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="30"/>
       <c r="L33" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="24" t="s">
+      <c r="M33" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="N33" s="25"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="26"/>
-    </row>
-    <row r="35" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="27"/>
+    </row>
+    <row r="35" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C35" s="15" t="s">
         <v>0</v>
       </c>
@@ -2324,7 +2364,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
@@ -2374,59 +2414,59 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="33"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="30"/>
       <c r="L37" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="24" t="s">
+      <c r="M37" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="26"/>
-    </row>
-    <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="27"/>
+    </row>
+    <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="33"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="30"/>
       <c r="L38" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="24" t="s">
+      <c r="M38" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="26"/>
-    </row>
-    <row r="40" spans="3:19" ht="28.9" x14ac:dyDescent="0.3">
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="27"/>
+    </row>
+    <row r="40" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
         <v>0</v>
       </c>
@@ -2476,7 +2516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C41" s="7" t="s">
         <v>75</v>
       </c>
@@ -2526,59 +2566,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
       <c r="L42" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="24" t="s">
+      <c r="M42" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
-      <c r="R42" s="25"/>
-      <c r="S42" s="26"/>
-    </row>
-    <row r="43" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="27"/>
+    </row>
+    <row r="43" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
       <c r="L43" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="24" t="s">
+      <c r="M43" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="25"/>
-      <c r="S43" s="26"/>
-    </row>
-    <row r="45" spans="3:19" ht="28.9" x14ac:dyDescent="0.3">
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="27"/>
+    </row>
+    <row r="45" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
         <v>0</v>
       </c>
@@ -2628,7 +2668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C46" s="7" t="s">
         <v>78</v>
       </c>
@@ -2678,59 +2718,59 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
       <c r="L47" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="24" t="s">
+      <c r="M47" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="25"/>
-      <c r="O47" s="25"/>
-      <c r="P47" s="25"/>
-      <c r="Q47" s="25"/>
-      <c r="R47" s="25"/>
-      <c r="S47" s="26"/>
-    </row>
-    <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="26"/>
+      <c r="S47" s="27"/>
+    </row>
+    <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
       <c r="L48" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="24" t="s">
+      <c r="M48" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="N48" s="25"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="25"/>
-      <c r="Q48" s="25"/>
-      <c r="R48" s="25"/>
-      <c r="S48" s="26"/>
-    </row>
-    <row r="50" spans="3:19" ht="28.9" x14ac:dyDescent="0.3">
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="27"/>
+    </row>
+    <row r="50" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
         <v>0</v>
       </c>
@@ -2780,7 +2820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C51" s="7" t="s">
         <v>102</v>
       </c>
@@ -2830,59 +2870,59 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
       <c r="L52" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="34" t="s">
+      <c r="M52" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
-    </row>
-    <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N52" s="33"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="33"/>
+    </row>
+    <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
       <c r="L53" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="34" t="s">
+      <c r="M53" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
-    </row>
-    <row r="55" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="33"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
         <v>0</v>
       </c>
@@ -2908,7 +2948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C56" s="7" t="s">
         <v>103</v>
       </c>
@@ -2934,35 +2974,35 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-    </row>
-    <row r="58" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C58" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-    </row>
-    <row r="60" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C60" s="7" t="s">
         <v>0</v>
       </c>
@@ -2988,7 +3028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="3:19" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C61" s="7" t="s">
         <v>82</v>
       </c>
@@ -3014,35 +3054,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-    </row>
-    <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+    </row>
+    <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-    </row>
-    <row r="65" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+    </row>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
         <v>0</v>
       </c>
@@ -3068,7 +3108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
         <v>85</v>
       </c>
@@ -3094,35 +3134,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="29"/>
-    </row>
-    <row r="68" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="36"/>
+    </row>
+    <row r="68" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="29"/>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="36"/>
+    </row>
+    <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="15" t="s">
         <v>0</v>
       </c>
@@ -3148,7 +3188,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C71" s="15" t="s">
         <v>88</v>
       </c>
@@ -3174,35 +3214,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="35" t="s">
+      <c r="D72" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-    </row>
-    <row r="73" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+    </row>
+    <row r="73" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-    </row>
-    <row r="75" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D73" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="31"/>
+      <c r="J73" s="31"/>
+    </row>
+    <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
         <v>0</v>
       </c>
@@ -3228,7 +3268,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C76" s="7" t="s">
         <v>90</v>
       </c>
@@ -3254,35 +3294,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C77" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-    </row>
-    <row r="78" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+    </row>
+    <row r="78" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C78" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-    </row>
-    <row r="80" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+    </row>
+    <row r="80" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C80" s="7" t="s">
         <v>0</v>
       </c>
@@ -3308,7 +3348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="7" t="s">
         <v>92</v>
       </c>
@@ -3334,35 +3374,35 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="27" t="s">
+      <c r="D82" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E82" s="28"/>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="29"/>
-    </row>
-    <row r="83" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="36"/>
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="27" t="s">
+      <c r="D83" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28"/>
-      <c r="J83" s="29"/>
-    </row>
-    <row r="85" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="36"/>
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="8" t="s">
         <v>0</v>
       </c>
@@ -3388,7 +3428,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="8" t="s">
         <v>94</v>
       </c>
@@ -3414,35 +3454,35 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C87" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21"/>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
-    </row>
-    <row r="88" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="22"/>
+      <c r="J87" s="22"/>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C88" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="E88" s="21"/>
-      <c r="F88" s="21"/>
-      <c r="G88" s="21"/>
-      <c r="H88" s="21"/>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21"/>
-    </row>
-    <row r="90" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
+    </row>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C90" s="9" t="s">
         <v>0</v>
       </c>
@@ -3468,7 +3508,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C91" s="9" t="s">
         <v>106</v>
       </c>
@@ -3494,35 +3534,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
-      <c r="I92" s="21"/>
-      <c r="J92" s="21"/>
-    </row>
-    <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="22"/>
+    </row>
+    <row r="93" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
-      <c r="I93" s="21"/>
-      <c r="J93" s="21"/>
-    </row>
-    <row r="95" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
+      <c r="J93" s="22"/>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="9" t="s">
         <v>0</v>
       </c>
@@ -3548,7 +3588,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="9" t="s">
         <v>109</v>
       </c>
@@ -3574,35 +3614,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21"/>
-    </row>
-    <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
+    </row>
+    <row r="98" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D98" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="E98" s="21"/>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="21"/>
-      <c r="J98" s="21"/>
-    </row>
-    <row r="100" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="9" t="s">
         <v>0</v>
       </c>
@@ -3628,7 +3668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C101" s="9" t="s">
         <v>113</v>
       </c>
@@ -3654,35 +3694,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C102" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="21" t="s">
+      <c r="D102" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21"/>
-    </row>
-    <row r="103" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="22"/>
+      <c r="J102" s="22"/>
+    </row>
+    <row r="103" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C103" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21"/>
-    </row>
-    <row r="105" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="22"/>
+      <c r="I103" s="22"/>
+      <c r="J103" s="22"/>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C105" s="16" t="s">
         <v>0</v>
       </c>
@@ -3708,7 +3748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C106" s="16" t="s">
         <v>121</v>
       </c>
@@ -3734,35 +3774,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C107" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-    </row>
-    <row r="108" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="22"/>
+    </row>
+    <row r="108" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C108" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="21" t="s">
+      <c r="D108" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E108" s="21"/>
-      <c r="F108" s="21"/>
-      <c r="G108" s="21"/>
-      <c r="H108" s="21"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
-    </row>
-    <row r="110" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="22"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="22"/>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C110" s="16" t="s">
         <v>0</v>
       </c>
@@ -3788,7 +3828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C111" s="16" t="s">
         <v>123</v>
       </c>
@@ -3814,35 +3854,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C112" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="21" t="s">
+      <c r="D112" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-    </row>
-    <row r="113" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
+      <c r="H112" s="22"/>
+      <c r="I112" s="22"/>
+      <c r="J112" s="22"/>
+    </row>
+    <row r="113" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C113" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="21" t="s">
+      <c r="D113" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21"/>
-    </row>
-    <row r="115" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="22"/>
+      <c r="H113" s="22"/>
+      <c r="I113" s="22"/>
+      <c r="J113" s="22"/>
+    </row>
+    <row r="115" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C115" s="16" t="s">
         <v>0</v>
       </c>
@@ -3868,7 +3908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C116" s="16" t="s">
         <v>126</v>
       </c>
@@ -3894,35 +3934,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="21" t="s">
+      <c r="D117" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E117" s="21"/>
-      <c r="F117" s="21"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
-      <c r="I117" s="21"/>
-      <c r="J117" s="21"/>
-    </row>
-    <row r="118" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
+      <c r="J117" s="22"/>
+    </row>
+    <row r="118" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C118" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="21" t="s">
+      <c r="D118" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E118" s="21"/>
-      <c r="F118" s="21"/>
-      <c r="G118" s="21"/>
-      <c r="H118" s="21"/>
-      <c r="I118" s="21"/>
-      <c r="J118" s="21"/>
-    </row>
-    <row r="120" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22"/>
+      <c r="I118" s="22"/>
+      <c r="J118" s="22"/>
+    </row>
+    <row r="120" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C120" s="16" t="s">
         <v>0</v>
       </c>
@@ -3948,7 +3988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C121" s="18" t="s">
         <v>129</v>
       </c>
@@ -3974,35 +4014,35 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="3:10" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="21" t="s">
+      <c r="D122" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E122" s="21"/>
-      <c r="F122" s="21"/>
-      <c r="G122" s="21"/>
-      <c r="H122" s="21"/>
-      <c r="I122" s="21"/>
-      <c r="J122" s="21"/>
-    </row>
-    <row r="123" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
+      <c r="I122" s="22"/>
+      <c r="J122" s="22"/>
+    </row>
+    <row r="123" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C123" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="21" t="s">
+      <c r="D123" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E123" s="21"/>
-      <c r="F123" s="21"/>
-      <c r="G123" s="21"/>
-      <c r="H123" s="21"/>
-      <c r="I123" s="21"/>
-      <c r="J123" s="21"/>
-    </row>
-    <row r="125" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="22"/>
+      <c r="J123" s="22"/>
+    </row>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C125" s="19" t="s">
         <v>0</v>
       </c>
@@ -4028,7 +4068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C126" s="19" t="s">
         <v>134</v>
       </c>
@@ -4054,35 +4094,35 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="3:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C127" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="21" t="s">
+      <c r="D127" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="E127" s="21"/>
-      <c r="F127" s="21"/>
-      <c r="G127" s="21"/>
-      <c r="H127" s="21"/>
-      <c r="I127" s="21"/>
-      <c r="J127" s="21"/>
-    </row>
-    <row r="128" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="22"/>
+      <c r="J127" s="22"/>
+    </row>
+    <row r="128" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C128" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="21" t="s">
+      <c r="D128" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="21"/>
-      <c r="F128" s="21"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="21"/>
-      <c r="I128" s="21"/>
-      <c r="J128" s="21"/>
-    </row>
-    <row r="130" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
+      <c r="J128" s="22"/>
+    </row>
+    <row r="130" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C130" s="19" t="s">
         <v>0</v>
       </c>
@@ -4108,7 +4148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C131" s="19" t="s">
         <v>135</v>
       </c>
@@ -4134,42 +4174,42 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C132" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="21" t="s">
+      <c r="D132" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E132" s="21"/>
-      <c r="F132" s="21"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
-      <c r="J132" s="21"/>
-    </row>
-    <row r="133" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
+    </row>
+    <row r="133" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="21" t="s">
+      <c r="D133" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-      <c r="I133" s="21"/>
-      <c r="J133" s="21"/>
-    </row>
-    <row r="134" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
+      <c r="J133" s="22"/>
+    </row>
+    <row r="134" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M134"/>
       <c r="N134"/>
       <c r="O134"/>
       <c r="P134"/>
       <c r="Q134"/>
     </row>
-    <row r="135" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C135" s="19" t="s">
         <v>0</v>
       </c>
@@ -4200,7 +4240,7 @@
       <c r="P135"/>
       <c r="Q135"/>
     </row>
-    <row r="136" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C136" s="19" t="s">
         <v>139</v>
       </c>
@@ -4231,52 +4271,52 @@
       <c r="P136"/>
       <c r="Q136"/>
     </row>
-    <row r="137" spans="3:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="21" t="s">
+      <c r="D137" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E137" s="21"/>
-      <c r="F137" s="21"/>
-      <c r="G137" s="21"/>
-      <c r="H137" s="21"/>
-      <c r="I137" s="21"/>
-      <c r="J137" s="21"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="22"/>
+      <c r="J137" s="22"/>
       <c r="M137"/>
       <c r="N137"/>
       <c r="O137"/>
       <c r="P137"/>
       <c r="Q137"/>
     </row>
-    <row r="138" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C138" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="21" t="s">
+      <c r="D138" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E138" s="21"/>
-      <c r="F138" s="21"/>
-      <c r="G138" s="21"/>
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
-      <c r="J138" s="21"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
       <c r="M138"/>
       <c r="N138"/>
       <c r="O138"/>
       <c r="P138"/>
       <c r="Q138"/>
     </row>
-    <row r="139" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M139"/>
       <c r="N139"/>
       <c r="O139"/>
       <c r="P139"/>
       <c r="Q139"/>
     </row>
-    <row r="140" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C140" s="19" t="s">
         <v>0</v>
       </c>
@@ -4307,7 +4347,7 @@
       <c r="P140"/>
       <c r="Q140"/>
     </row>
-    <row r="141" spans="3:17" ht="47.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:17" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="19" t="s">
         <v>142</v>
       </c>
@@ -4337,31 +4377,31 @@
       <c r="C142" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="21" t="s">
+      <c r="D142" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
-      <c r="I142" s="21"/>
-      <c r="J142" s="21"/>
-    </row>
-    <row r="143" spans="3:17" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E142" s="22"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22"/>
+      <c r="I142" s="22"/>
+      <c r="J142" s="22"/>
+    </row>
+    <row r="143" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C143" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="21" t="s">
+      <c r="D143" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
-      <c r="I143" s="21"/>
-      <c r="J143" s="21"/>
-    </row>
-    <row r="145" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E143" s="22"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22"/>
+      <c r="I143" s="22"/>
+      <c r="J143" s="22"/>
+    </row>
+    <row r="145" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C145" s="19" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4427,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C146" s="19" t="s">
         <v>147</v>
       </c>
@@ -4413,35 +4453,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C147" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="21" t="s">
+      <c r="D147" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
-      <c r="I147" s="21"/>
-      <c r="J147" s="21"/>
-    </row>
-    <row r="148" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E147" s="22"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22"/>
+      <c r="I147" s="22"/>
+      <c r="J147" s="22"/>
+    </row>
+    <row r="148" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C148" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="21" t="s">
+      <c r="D148" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="E148" s="21"/>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
-      <c r="I148" s="21"/>
-      <c r="J148" s="21"/>
-    </row>
-    <row r="150" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E148" s="22"/>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22"/>
+      <c r="I148" s="22"/>
+      <c r="J148" s="22"/>
+    </row>
+    <row r="150" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C150" s="19" t="s">
         <v>0</v>
       </c>
@@ -4467,7 +4507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C151" s="19" t="s">
         <v>150</v>
       </c>
@@ -4493,35 +4533,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C152" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D152" s="21" t="s">
+      <c r="D152" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="E152" s="21"/>
-      <c r="F152" s="21"/>
-      <c r="G152" s="21"/>
-      <c r="H152" s="21"/>
-      <c r="I152" s="21"/>
-      <c r="J152" s="21"/>
-    </row>
-    <row r="153" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E152" s="22"/>
+      <c r="F152" s="22"/>
+      <c r="G152" s="22"/>
+      <c r="H152" s="22"/>
+      <c r="I152" s="22"/>
+      <c r="J152" s="22"/>
+    </row>
+    <row r="153" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C153" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D153" s="21" t="s">
+      <c r="D153" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="E153" s="21"/>
-      <c r="F153" s="21"/>
-      <c r="G153" s="21"/>
-      <c r="H153" s="21"/>
-      <c r="I153" s="21"/>
-      <c r="J153" s="21"/>
-    </row>
-    <row r="155" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E153" s="22"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
+      <c r="H153" s="22"/>
+      <c r="I153" s="22"/>
+      <c r="J153" s="22"/>
+    </row>
+    <row r="155" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C155" s="20" t="s">
         <v>0</v>
       </c>
@@ -4547,7 +4587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C156" s="20" t="s">
         <v>153</v>
       </c>
@@ -4564,7 +4604,7 @@
         <v>7</v>
       </c>
       <c r="H156" s="20" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I156" s="20" t="s">
         <v>37</v>
@@ -4573,35 +4613,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C157" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D157" s="21" t="s">
+      <c r="D157" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="E157" s="21"/>
-      <c r="F157" s="21"/>
-      <c r="G157" s="21"/>
-      <c r="H157" s="21"/>
-      <c r="I157" s="21"/>
-      <c r="J157" s="21"/>
-    </row>
-    <row r="158" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="E157" s="22"/>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22"/>
+      <c r="H157" s="22"/>
+      <c r="I157" s="22"/>
+      <c r="J157" s="22"/>
+    </row>
+    <row r="158" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C158" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D158" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E158" s="21"/>
-      <c r="F158" s="21"/>
-      <c r="G158" s="21"/>
-      <c r="H158" s="21"/>
-      <c r="I158" s="21"/>
-      <c r="J158" s="21"/>
-    </row>
-    <row r="160" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D158" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E158" s="22"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22"/>
+      <c r="H158" s="22"/>
+      <c r="I158" s="22"/>
+      <c r="J158" s="22"/>
+    </row>
+    <row r="160" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C160" s="20" t="s">
         <v>0</v>
       </c>
@@ -4627,15 +4667,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C161" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D161" s="20">
         <v>3</v>
       </c>
       <c r="E161" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="20" t="s">
         <v>22</v>
@@ -4644,44 +4684,44 @@
         <v>7</v>
       </c>
       <c r="H161" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I161" s="20" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="I161" s="21" t="s">
+        <v>57</v>
       </c>
       <c r="J161" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="162" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C162" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D162" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E162" s="21"/>
-      <c r="F162" s="21"/>
-      <c r="G162" s="21"/>
-      <c r="H162" s="21"/>
-      <c r="I162" s="21"/>
-      <c r="J162" s="21"/>
-    </row>
-    <row r="163" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D162" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E162" s="22"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
+      <c r="H162" s="22"/>
+      <c r="I162" s="22"/>
+      <c r="J162" s="22"/>
+    </row>
+    <row r="163" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C163" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D163" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E163" s="21"/>
-      <c r="F163" s="21"/>
-      <c r="G163" s="21"/>
-      <c r="H163" s="21"/>
-      <c r="I163" s="21"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="165" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D163" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E163" s="22"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22"/>
+      <c r="H163" s="22"/>
+      <c r="I163" s="22"/>
+      <c r="J163" s="22"/>
+    </row>
+    <row r="165" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C165" s="20" t="s">
         <v>0</v>
       </c>
@@ -4706,10 +4746,18 @@
       <c r="J165" s="20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="166" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C166" s="20">
-        <v>3</v>
+      <c r="L165"/>
+      <c r="M165"/>
+      <c r="N165"/>
+      <c r="O165"/>
+      <c r="P165"/>
+      <c r="Q165"/>
+      <c r="R165"/>
+      <c r="S165"/>
+    </row>
+    <row r="166" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C166" s="20" t="s">
+        <v>166</v>
       </c>
       <c r="D166" s="20">
         <v>3</v>
@@ -4718,50 +4766,74 @@
         <v>1</v>
       </c>
       <c r="F166" s="20" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G166" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H166" s="20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J166" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="167" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="L166"/>
+      <c r="M166"/>
+      <c r="N166"/>
+      <c r="O166"/>
+      <c r="P166"/>
+      <c r="Q166"/>
+      <c r="R166"/>
+      <c r="S166"/>
+    </row>
+    <row r="167" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C167" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D167" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E167" s="21"/>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-      <c r="H167" s="21"/>
-      <c r="I167" s="21"/>
-      <c r="J167" s="21"/>
-    </row>
-    <row r="168" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D167" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
+      <c r="L167"/>
+      <c r="M167" s="37"/>
+      <c r="N167" s="37"/>
+      <c r="O167" s="37"/>
+      <c r="P167" s="37"/>
+      <c r="Q167" s="37"/>
+      <c r="R167" s="37"/>
+      <c r="S167" s="37"/>
+    </row>
+    <row r="168" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C168" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D168" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E168" s="21"/>
-      <c r="F168" s="21"/>
-      <c r="G168" s="21"/>
-      <c r="H168" s="21"/>
-      <c r="I168" s="21"/>
-      <c r="J168" s="21"/>
-    </row>
-    <row r="170" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D168" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E168" s="22"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
+      <c r="H168" s="22"/>
+      <c r="I168" s="22"/>
+      <c r="J168" s="22"/>
+      <c r="L168"/>
+      <c r="M168" s="37"/>
+      <c r="N168" s="37"/>
+      <c r="O168" s="37"/>
+      <c r="P168" s="37"/>
+      <c r="Q168" s="37"/>
+      <c r="R168" s="37"/>
+      <c r="S168" s="37"/>
+    </row>
+    <row r="170" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C170" s="20" t="s">
         <v>0</v>
       </c>
@@ -4787,61 +4859,61 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C171" s="20">
-        <v>4</v>
+    <row r="171" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C171" s="20" t="s">
+        <v>168</v>
       </c>
       <c r="D171" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G171" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H171" s="20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I171" s="20" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J171" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="172" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="172" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C172" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D172" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E172" s="21"/>
-      <c r="F172" s="21"/>
-      <c r="G172" s="21"/>
-      <c r="H172" s="21"/>
-      <c r="I172" s="21"/>
-      <c r="J172" s="21"/>
-    </row>
-    <row r="173" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="D172" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="E172" s="22"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
+      <c r="H172" s="22"/>
+      <c r="I172" s="22"/>
+      <c r="J172" s="22"/>
+    </row>
+    <row r="173" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C173" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D173" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E173" s="21"/>
-      <c r="F173" s="21"/>
-      <c r="G173" s="21"/>
-      <c r="H173" s="21"/>
-      <c r="I173" s="21"/>
-      <c r="J173" s="21"/>
-    </row>
-    <row r="175" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D173" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E173" s="22"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
+      <c r="H173" s="22"/>
+      <c r="I173" s="22"/>
+      <c r="J173" s="22"/>
+    </row>
+    <row r="175" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C175" s="20" t="s">
         <v>0</v>
       </c>
@@ -4867,9 +4939,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C176" s="20">
-        <v>5</v>
+    <row r="176" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C176" s="20" t="s">
+        <v>172</v>
       </c>
       <c r="D176" s="20">
         <v>3</v>
@@ -4878,51 +4950,137 @@
         <v>1</v>
       </c>
       <c r="F176" s="20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G176" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H176" s="20" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="I176" s="20" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J176" s="20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="177" spans="3:10" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C177" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D177" s="21" t="s">
+      <c r="D177" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="E177" s="21"/>
-      <c r="F177" s="21"/>
-      <c r="G177" s="21"/>
-      <c r="H177" s="21"/>
-      <c r="I177" s="21"/>
-      <c r="J177" s="21"/>
-    </row>
-    <row r="178" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
+      <c r="H177" s="22"/>
+      <c r="I177" s="22"/>
+      <c r="J177" s="22"/>
+    </row>
+    <row r="178" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C178" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E178" s="21"/>
-      <c r="F178" s="21"/>
-      <c r="G178" s="21"/>
-      <c r="H178" s="21"/>
-      <c r="I178" s="21"/>
-      <c r="J178" s="21"/>
+      <c r="D178" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E178" s="22"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
+      <c r="H178" s="22"/>
+      <c r="I178" s="22"/>
+      <c r="J178" s="22"/>
+    </row>
+    <row r="180" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C180" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D180" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E180" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F180" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="H180" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="I180" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J180" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C181" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D181" s="21">
+        <v>3</v>
+      </c>
+      <c r="E181" s="21">
+        <v>1</v>
+      </c>
+      <c r="F181" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G181" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I181" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J181" s="21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="182" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C182" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E182" s="22"/>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22"/>
+      <c r="H182" s="22"/>
+      <c r="I182" s="22"/>
+      <c r="J182" s="22"/>
+    </row>
+    <row r="183" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C183" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E183" s="22"/>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22"/>
+      <c r="H183" s="22"/>
+      <c r="I183" s="22"/>
+      <c r="J183" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="97">
+  <mergeCells count="101">
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
     <mergeCell ref="D118:J118"/>
     <mergeCell ref="D122:J122"/>
     <mergeCell ref="D123:J123"/>
@@ -4931,12 +5089,11 @@
     <mergeCell ref="D112:J112"/>
     <mergeCell ref="D113:J113"/>
     <mergeCell ref="D117:J117"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D67:J67"/>
     <mergeCell ref="D68:J68"/>
     <mergeCell ref="D83:J83"/>
     <mergeCell ref="D72:J72"/>
@@ -4944,11 +5101,9 @@
     <mergeCell ref="D77:J77"/>
     <mergeCell ref="D78:J78"/>
     <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M38:S38"/>
     <mergeCell ref="M53:S53"/>
     <mergeCell ref="D17:J17"/>
     <mergeCell ref="D18:J18"/>
@@ -4965,12 +5120,6 @@
     <mergeCell ref="M47:S47"/>
     <mergeCell ref="M48:S48"/>
     <mergeCell ref="M52:S52"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M38:S38"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="V12:AB12"/>
     <mergeCell ref="V13:AB13"/>
@@ -4982,6 +5131,11 @@
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="D137:J137"/>
     <mergeCell ref="D87:J87"/>
     <mergeCell ref="D88:J88"/>
     <mergeCell ref="M22:S22"/>
@@ -4998,11 +5152,14 @@
     <mergeCell ref="M23:S23"/>
     <mergeCell ref="D27:J27"/>
     <mergeCell ref="M27:S27"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D167:J167"/>
     <mergeCell ref="D152:J152"/>
     <mergeCell ref="D153:J153"/>
     <mergeCell ref="D138:J138"/>
@@ -5010,11 +5167,10 @@
     <mergeCell ref="D143:J143"/>
     <mergeCell ref="D147:J147"/>
     <mergeCell ref="D148:J148"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D167:J167"/>
+    <mergeCell ref="D182:J182"/>
+    <mergeCell ref="D183:J183"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
     <mergeCell ref="D168:J168"/>
     <mergeCell ref="D172:J172"/>
     <mergeCell ref="D173:J173"/>
@@ -5029,42 +5185,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="30"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5078,7 +5234,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="177">
   <si>
     <t>Name</t>
   </si>
@@ -538,6 +538,15 @@
   </si>
   <si>
     <t>Evading, Merging</t>
+  </si>
+  <si>
+    <t>Bladesinger</t>
+  </si>
+  <si>
+    <t>Bladeguarded</t>
+  </si>
+  <si>
+    <t>Old drukhari baasic troop</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -746,10 +755,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -761,31 +788,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1094,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB183"/>
+  <dimension ref="A1:AB188"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -1116,30 +1128,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1335,27 +1347,27 @@
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="24" t="s">
+      <c r="V7" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
     </row>
     <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
@@ -1377,27 +1389,27 @@
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="24" t="s">
+      <c r="V8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="36"/>
+      <c r="AB8" s="36"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1567,65 +1579,65 @@
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="24" t="s">
+      <c r="V12" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
     </row>
     <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="24" t="s">
+      <c r="V13" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O14"/>
@@ -1783,77 +1795,77 @@
       <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="M17" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="24" t="s">
+      <c r="V17" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="36"/>
+      <c r="Y17" s="36"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="36"/>
+      <c r="AB17" s="36"/>
     </row>
     <row r="18" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="M18" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="37"/>
+      <c r="S18" s="37"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="24" t="s">
+      <c r="V18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="36"/>
     </row>
     <row r="19" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="O19"/>
@@ -1962,53 +1974,53 @@
       <c r="C22" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="23" t="s">
+      <c r="M22" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
     </row>
     <row r="25" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="15" t="s">
@@ -2114,53 +2126,53 @@
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
     </row>
     <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="22" t="s">
+      <c r="M28" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
     </row>
     <row r="30" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C30" s="15" t="s">
@@ -2278,15 +2290,15 @@
       <c r="L32" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="25" t="s">
+      <c r="M32" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="27"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="33"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="15" t="s">
@@ -2304,15 +2316,15 @@
       <c r="L33" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="25" t="s">
+      <c r="M33" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="27"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="33"/>
     </row>
     <row r="35" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C35" s="15" t="s">
@@ -2430,15 +2442,15 @@
       <c r="L37" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="25" t="s">
+      <c r="M37" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="27"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="33"/>
     </row>
     <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="15" t="s">
@@ -2456,15 +2468,15 @@
       <c r="L38" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="27"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="33"/>
     </row>
     <row r="40" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
@@ -2570,53 +2582,53 @@
       <c r="C42" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
       <c r="L42" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="25" t="s">
+      <c r="M42" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="27"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="33"/>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
       <c r="L43" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="25" t="s">
+      <c r="M43" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="27"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="33"/>
     </row>
     <row r="45" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
@@ -2722,53 +2734,53 @@
       <c r="C47" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
       <c r="L47" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="25" t="s">
+      <c r="M47" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="26"/>
-      <c r="S47" s="27"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="33"/>
     </row>
     <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
       <c r="L48" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="25" t="s">
+      <c r="M48" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="27"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="33"/>
     </row>
     <row r="50" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
@@ -2874,53 +2886,53 @@
       <c r="C52" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
       <c r="L52" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="33" t="s">
+      <c r="M52" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="33"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="33"/>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="34"/>
+      <c r="Q52" s="34"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="34"/>
     </row>
     <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="23"/>
+      <c r="J53" s="23"/>
       <c r="L53" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="33" t="s">
+      <c r="M53" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="33"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
@@ -2978,29 +2990,29 @@
       <c r="C57" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="23"/>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C58" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C60" s="7" t="s">
@@ -3058,29 +3070,29 @@
       <c r="C62" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
     </row>
     <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="23"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
@@ -3138,29 +3150,29 @@
       <c r="C67" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="36"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="26"/>
     </row>
     <row r="68" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="34" t="s">
+      <c r="D68" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="36"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="26"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="15" t="s">
@@ -3218,29 +3230,29 @@
       <c r="C72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
+      <c r="J72" s="27"/>
     </row>
     <row r="73" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="31"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
@@ -3298,29 +3310,29 @@
       <c r="C77" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="23"/>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C78" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="22"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C80" s="7" t="s">
@@ -3378,29 +3390,29 @@
       <c r="C82" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="34" t="s">
+      <c r="D82" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="36"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="26"/>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="34" t="s">
+      <c r="D83" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="36"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="26"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="8" t="s">
@@ -3458,29 +3470,29 @@
       <c r="C87" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="22" t="s">
+      <c r="D87" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="22"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
+      <c r="I87" s="23"/>
+      <c r="J87" s="23"/>
     </row>
     <row r="88" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C88" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="22" t="s">
+      <c r="D88" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="E88" s="22"/>
-      <c r="F88" s="22"/>
-      <c r="G88" s="22"/>
-      <c r="H88" s="22"/>
-      <c r="I88" s="22"/>
-      <c r="J88" s="22"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
     </row>
     <row r="90" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C90" s="9" t="s">
@@ -3538,29 +3550,29 @@
       <c r="C92" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="22" t="s">
+      <c r="D92" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-      <c r="I92" s="22"/>
-      <c r="J92" s="22"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="23"/>
+      <c r="J92" s="23"/>
     </row>
     <row r="93" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="23"/>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="9" t="s">
@@ -3618,29 +3630,29 @@
       <c r="C97" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="22" t="s">
+      <c r="D97" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="22"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="22"/>
-      <c r="J97" s="22"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
     </row>
     <row r="98" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="22" t="s">
+      <c r="D98" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23"/>
     </row>
     <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="9" t="s">
@@ -3698,29 +3710,29 @@
       <c r="C102" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="22" t="s">
+      <c r="D102" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
-      <c r="H102" s="22"/>
-      <c r="I102" s="22"/>
-      <c r="J102" s="22"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
     </row>
     <row r="103" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C103" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="22" t="s">
+      <c r="D103" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="E103" s="22"/>
-      <c r="F103" s="22"/>
-      <c r="G103" s="22"/>
-      <c r="H103" s="22"/>
-      <c r="I103" s="22"/>
-      <c r="J103" s="22"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+      <c r="G103" s="23"/>
+      <c r="H103" s="23"/>
+      <c r="I103" s="23"/>
+      <c r="J103" s="23"/>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C105" s="16" t="s">
@@ -3778,29 +3790,29 @@
       <c r="C107" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="22" t="s">
+      <c r="D107" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="E107" s="22"/>
-      <c r="F107" s="22"/>
-      <c r="G107" s="22"/>
-      <c r="H107" s="22"/>
-      <c r="I107" s="22"/>
-      <c r="J107" s="22"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
     </row>
     <row r="108" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C108" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="22" t="s">
+      <c r="D108" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="E108" s="22"/>
-      <c r="F108" s="22"/>
-      <c r="G108" s="22"/>
-      <c r="H108" s="22"/>
-      <c r="I108" s="22"/>
-      <c r="J108" s="22"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C110" s="16" t="s">
@@ -3858,29 +3870,29 @@
       <c r="C112" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D112" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22"/>
-      <c r="G112" s="22"/>
-      <c r="H112" s="22"/>
-      <c r="I112" s="22"/>
-      <c r="J112" s="22"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
     </row>
     <row r="113" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C113" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D113" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="E113" s="22"/>
-      <c r="F113" s="22"/>
-      <c r="G113" s="22"/>
-      <c r="H113" s="22"/>
-      <c r="I113" s="22"/>
-      <c r="J113" s="22"/>
+      <c r="E113" s="23"/>
+      <c r="F113" s="23"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+      <c r="J113" s="23"/>
     </row>
     <row r="115" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C115" s="16" t="s">
@@ -3938,29 +3950,29 @@
       <c r="C117" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="22" t="s">
+      <c r="D117" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="E117" s="22"/>
-      <c r="F117" s="22"/>
-      <c r="G117" s="22"/>
-      <c r="H117" s="22"/>
-      <c r="I117" s="22"/>
-      <c r="J117" s="22"/>
+      <c r="E117" s="23"/>
+      <c r="F117" s="23"/>
+      <c r="G117" s="23"/>
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
+      <c r="J117" s="23"/>
     </row>
     <row r="118" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C118" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="D118" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="E118" s="22"/>
-      <c r="F118" s="22"/>
-      <c r="G118" s="22"/>
-      <c r="H118" s="22"/>
-      <c r="I118" s="22"/>
-      <c r="J118" s="22"/>
+      <c r="E118" s="23"/>
+      <c r="F118" s="23"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23"/>
     </row>
     <row r="120" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C120" s="16" t="s">
@@ -4018,29 +4030,29 @@
       <c r="C122" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="22" t="s">
+      <c r="D122" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="E122" s="22"/>
-      <c r="F122" s="22"/>
-      <c r="G122" s="22"/>
-      <c r="H122" s="22"/>
-      <c r="I122" s="22"/>
-      <c r="J122" s="22"/>
+      <c r="E122" s="23"/>
+      <c r="F122" s="23"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="23"/>
+      <c r="I122" s="23"/>
+      <c r="J122" s="23"/>
     </row>
     <row r="123" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C123" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="22" t="s">
+      <c r="D123" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22"/>
-      <c r="G123" s="22"/>
-      <c r="H123" s="22"/>
-      <c r="I123" s="22"/>
-      <c r="J123" s="22"/>
+      <c r="E123" s="23"/>
+      <c r="F123" s="23"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="23"/>
     </row>
     <row r="125" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C125" s="19" t="s">
@@ -4098,29 +4110,29 @@
       <c r="C127" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="22" t="s">
+      <c r="D127" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="E127" s="22"/>
-      <c r="F127" s="22"/>
-      <c r="G127" s="22"/>
-      <c r="H127" s="22"/>
-      <c r="I127" s="22"/>
-      <c r="J127" s="22"/>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="23"/>
     </row>
     <row r="128" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C128" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="22" t="s">
+      <c r="D128" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="22"/>
-      <c r="J128" s="22"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="23"/>
     </row>
     <row r="130" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C130" s="19" t="s">
@@ -4178,29 +4190,29 @@
       <c r="C132" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D132" s="22" t="s">
+      <c r="D132" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="22"/>
+      <c r="E132" s="23"/>
+      <c r="F132" s="23"/>
+      <c r="G132" s="23"/>
+      <c r="H132" s="23"/>
+      <c r="I132" s="23"/>
+      <c r="J132" s="23"/>
     </row>
     <row r="133" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D133" s="22" t="s">
+      <c r="D133" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
-      <c r="G133" s="22"/>
-      <c r="H133" s="22"/>
-      <c r="I133" s="22"/>
-      <c r="J133" s="22"/>
+      <c r="E133" s="23"/>
+      <c r="F133" s="23"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="23"/>
+      <c r="I133" s="23"/>
+      <c r="J133" s="23"/>
     </row>
     <row r="134" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M134"/>
@@ -4275,15 +4287,15 @@
       <c r="C137" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="22" t="s">
+      <c r="D137" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="22"/>
-      <c r="H137" s="22"/>
-      <c r="I137" s="22"/>
-      <c r="J137" s="22"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
       <c r="M137"/>
       <c r="N137"/>
       <c r="O137"/>
@@ -4294,15 +4306,15 @@
       <c r="C138" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="22" t="s">
+      <c r="D138" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="22"/>
-      <c r="H138" s="22"/>
-      <c r="I138" s="22"/>
-      <c r="J138" s="22"/>
+      <c r="E138" s="23"/>
+      <c r="F138" s="23"/>
+      <c r="G138" s="23"/>
+      <c r="H138" s="23"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="23"/>
       <c r="M138"/>
       <c r="N138"/>
       <c r="O138"/>
@@ -4377,29 +4389,29 @@
       <c r="C142" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="22" t="s">
+      <c r="D142" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="E142" s="22"/>
-      <c r="F142" s="22"/>
-      <c r="G142" s="22"/>
-      <c r="H142" s="22"/>
-      <c r="I142" s="22"/>
-      <c r="J142" s="22"/>
+      <c r="E142" s="23"/>
+      <c r="F142" s="23"/>
+      <c r="G142" s="23"/>
+      <c r="H142" s="23"/>
+      <c r="I142" s="23"/>
+      <c r="J142" s="23"/>
     </row>
     <row r="143" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C143" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="22" t="s">
+      <c r="D143" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
-      <c r="G143" s="22"/>
-      <c r="H143" s="22"/>
-      <c r="I143" s="22"/>
-      <c r="J143" s="22"/>
+      <c r="E143" s="23"/>
+      <c r="F143" s="23"/>
+      <c r="G143" s="23"/>
+      <c r="H143" s="23"/>
+      <c r="I143" s="23"/>
+      <c r="J143" s="23"/>
     </row>
     <row r="145" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C145" s="19" t="s">
@@ -4457,29 +4469,29 @@
       <c r="C147" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="22" t="s">
+      <c r="D147" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
-      <c r="G147" s="22"/>
-      <c r="H147" s="22"/>
-      <c r="I147" s="22"/>
-      <c r="J147" s="22"/>
+      <c r="E147" s="23"/>
+      <c r="F147" s="23"/>
+      <c r="G147" s="23"/>
+      <c r="H147" s="23"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="23"/>
     </row>
     <row r="148" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C148" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="22" t="s">
+      <c r="D148" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
-      <c r="G148" s="22"/>
-      <c r="H148" s="22"/>
-      <c r="I148" s="22"/>
-      <c r="J148" s="22"/>
+      <c r="E148" s="23"/>
+      <c r="F148" s="23"/>
+      <c r="G148" s="23"/>
+      <c r="H148" s="23"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="23"/>
     </row>
     <row r="150" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C150" s="19" t="s">
@@ -4537,29 +4549,29 @@
       <c r="C152" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D152" s="22" t="s">
+      <c r="D152" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="E152" s="22"/>
-      <c r="F152" s="22"/>
-      <c r="G152" s="22"/>
-      <c r="H152" s="22"/>
-      <c r="I152" s="22"/>
-      <c r="J152" s="22"/>
+      <c r="E152" s="23"/>
+      <c r="F152" s="23"/>
+      <c r="G152" s="23"/>
+      <c r="H152" s="23"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="23"/>
     </row>
     <row r="153" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C153" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D153" s="22" t="s">
+      <c r="D153" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="E153" s="22"/>
-      <c r="F153" s="22"/>
-      <c r="G153" s="22"/>
-      <c r="H153" s="22"/>
-      <c r="I153" s="22"/>
-      <c r="J153" s="22"/>
+      <c r="E153" s="23"/>
+      <c r="F153" s="23"/>
+      <c r="G153" s="23"/>
+      <c r="H153" s="23"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="23"/>
     </row>
     <row r="155" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C155" s="20" t="s">
@@ -4617,29 +4629,29 @@
       <c r="C157" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D157" s="22" t="s">
+      <c r="D157" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E157" s="22"/>
-      <c r="F157" s="22"/>
-      <c r="G157" s="22"/>
-      <c r="H157" s="22"/>
-      <c r="I157" s="22"/>
-      <c r="J157" s="22"/>
+      <c r="E157" s="23"/>
+      <c r="F157" s="23"/>
+      <c r="G157" s="23"/>
+      <c r="H157" s="23"/>
+      <c r="I157" s="23"/>
+      <c r="J157" s="23"/>
     </row>
     <row r="158" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C158" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D158" s="22" t="s">
+      <c r="D158" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E158" s="22"/>
-      <c r="F158" s="22"/>
-      <c r="G158" s="22"/>
-      <c r="H158" s="22"/>
-      <c r="I158" s="22"/>
-      <c r="J158" s="22"/>
+      <c r="E158" s="23"/>
+      <c r="F158" s="23"/>
+      <c r="G158" s="23"/>
+      <c r="H158" s="23"/>
+      <c r="I158" s="23"/>
+      <c r="J158" s="23"/>
     </row>
     <row r="160" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C160" s="20" t="s">
@@ -4697,29 +4709,29 @@
       <c r="C162" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D162" s="22" t="s">
+      <c r="D162" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="E162" s="22"/>
-      <c r="F162" s="22"/>
-      <c r="G162" s="22"/>
-      <c r="H162" s="22"/>
-      <c r="I162" s="22"/>
-      <c r="J162" s="22"/>
+      <c r="E162" s="23"/>
+      <c r="F162" s="23"/>
+      <c r="G162" s="23"/>
+      <c r="H162" s="23"/>
+      <c r="I162" s="23"/>
+      <c r="J162" s="23"/>
     </row>
     <row r="163" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C163" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D163" s="22" t="s">
+      <c r="D163" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E163" s="22"/>
-      <c r="F163" s="22"/>
-      <c r="G163" s="22"/>
-      <c r="H163" s="22"/>
-      <c r="I163" s="22"/>
-      <c r="J163" s="22"/>
+      <c r="E163" s="23"/>
+      <c r="F163" s="23"/>
+      <c r="G163" s="23"/>
+      <c r="H163" s="23"/>
+      <c r="I163" s="23"/>
+      <c r="J163" s="23"/>
     </row>
     <row r="165" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C165" s="20" t="s">
@@ -4793,45 +4805,45 @@
       <c r="C167" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D167" s="22" t="s">
+      <c r="D167" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="E167" s="22"/>
-      <c r="F167" s="22"/>
-      <c r="G167" s="22"/>
-      <c r="H167" s="22"/>
-      <c r="I167" s="22"/>
-      <c r="J167" s="22"/>
+      <c r="E167" s="23"/>
+      <c r="F167" s="23"/>
+      <c r="G167" s="23"/>
+      <c r="H167" s="23"/>
+      <c r="I167" s="23"/>
+      <c r="J167" s="23"/>
       <c r="L167"/>
-      <c r="M167" s="37"/>
-      <c r="N167" s="37"/>
-      <c r="O167" s="37"/>
-      <c r="P167" s="37"/>
-      <c r="Q167" s="37"/>
-      <c r="R167" s="37"/>
-      <c r="S167" s="37"/>
+      <c r="M167" s="38"/>
+      <c r="N167" s="38"/>
+      <c r="O167" s="38"/>
+      <c r="P167" s="38"/>
+      <c r="Q167" s="38"/>
+      <c r="R167" s="38"/>
+      <c r="S167" s="38"/>
     </row>
     <row r="168" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C168" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D168" s="22" t="s">
+      <c r="D168" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="E168" s="22"/>
-      <c r="F168" s="22"/>
-      <c r="G168" s="22"/>
-      <c r="H168" s="22"/>
-      <c r="I168" s="22"/>
-      <c r="J168" s="22"/>
+      <c r="E168" s="23"/>
+      <c r="F168" s="23"/>
+      <c r="G168" s="23"/>
+      <c r="H168" s="23"/>
+      <c r="I168" s="23"/>
+      <c r="J168" s="23"/>
       <c r="L168"/>
-      <c r="M168" s="37"/>
-      <c r="N168" s="37"/>
-      <c r="O168" s="37"/>
-      <c r="P168" s="37"/>
-      <c r="Q168" s="37"/>
-      <c r="R168" s="37"/>
-      <c r="S168" s="37"/>
+      <c r="M168" s="38"/>
+      <c r="N168" s="38"/>
+      <c r="O168" s="38"/>
+      <c r="P168" s="38"/>
+      <c r="Q168" s="38"/>
+      <c r="R168" s="38"/>
+      <c r="S168" s="38"/>
     </row>
     <row r="170" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C170" s="20" t="s">
@@ -4889,29 +4901,29 @@
       <c r="C172" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D172" s="22" t="s">
+      <c r="D172" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="E172" s="22"/>
-      <c r="F172" s="22"/>
-      <c r="G172" s="22"/>
-      <c r="H172" s="22"/>
-      <c r="I172" s="22"/>
-      <c r="J172" s="22"/>
+      <c r="E172" s="23"/>
+      <c r="F172" s="23"/>
+      <c r="G172" s="23"/>
+      <c r="H172" s="23"/>
+      <c r="I172" s="23"/>
+      <c r="J172" s="23"/>
     </row>
     <row r="173" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C173" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D173" s="22" t="s">
+      <c r="D173" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="E173" s="22"/>
-      <c r="F173" s="22"/>
-      <c r="G173" s="22"/>
-      <c r="H173" s="22"/>
-      <c r="I173" s="22"/>
-      <c r="J173" s="22"/>
+      <c r="E173" s="23"/>
+      <c r="F173" s="23"/>
+      <c r="G173" s="23"/>
+      <c r="H173" s="23"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="23"/>
     </row>
     <row r="175" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C175" s="20" t="s">
@@ -4969,29 +4981,29 @@
       <c r="C177" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D177" s="22" t="s">
+      <c r="D177" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E177" s="22"/>
-      <c r="F177" s="22"/>
-      <c r="G177" s="22"/>
-      <c r="H177" s="22"/>
-      <c r="I177" s="22"/>
-      <c r="J177" s="22"/>
+      <c r="E177" s="23"/>
+      <c r="F177" s="23"/>
+      <c r="G177" s="23"/>
+      <c r="H177" s="23"/>
+      <c r="I177" s="23"/>
+      <c r="J177" s="23"/>
     </row>
     <row r="178" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C178" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="22" t="s">
+      <c r="D178" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="E178" s="22"/>
-      <c r="F178" s="22"/>
-      <c r="G178" s="22"/>
-      <c r="H178" s="22"/>
-      <c r="I178" s="22"/>
-      <c r="J178" s="22"/>
+      <c r="E178" s="23"/>
+      <c r="F178" s="23"/>
+      <c r="G178" s="23"/>
+      <c r="H178" s="23"/>
+      <c r="I178" s="23"/>
+      <c r="J178" s="23"/>
     </row>
     <row r="180" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C180" s="21" t="s">
@@ -5049,88 +5061,135 @@
       <c r="C182" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D182" s="22" t="s">
+      <c r="D182" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="E182" s="22"/>
-      <c r="F182" s="22"/>
-      <c r="G182" s="22"/>
-      <c r="H182" s="22"/>
-      <c r="I182" s="22"/>
-      <c r="J182" s="22"/>
+      <c r="E182" s="23"/>
+      <c r="F182" s="23"/>
+      <c r="G182" s="23"/>
+      <c r="H182" s="23"/>
+      <c r="I182" s="23"/>
+      <c r="J182" s="23"/>
     </row>
     <row r="183" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C183" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D183" s="22" t="s">
+      <c r="D183" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="E183" s="22"/>
-      <c r="F183" s="22"/>
-      <c r="G183" s="22"/>
-      <c r="H183" s="22"/>
-      <c r="I183" s="22"/>
-      <c r="J183" s="22"/>
+      <c r="E183" s="23"/>
+      <c r="F183" s="23"/>
+      <c r="G183" s="23"/>
+      <c r="H183" s="23"/>
+      <c r="I183" s="23"/>
+      <c r="J183" s="23"/>
+    </row>
+    <row r="185" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C185" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D185" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E185" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F185" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="H185" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I185" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="J185" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C186" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D186" s="22">
+        <v>3</v>
+      </c>
+      <c r="E186" s="22">
+        <v>1</v>
+      </c>
+      <c r="F186" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I186" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J186" s="22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="187" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C187" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D187" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E187" s="23"/>
+      <c r="F187" s="23"/>
+      <c r="G187" s="23"/>
+      <c r="H187" s="23"/>
+      <c r="I187" s="23"/>
+      <c r="J187" s="23"/>
+    </row>
+    <row r="188" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C188" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="E188" s="23"/>
+      <c r="F188" s="23"/>
+      <c r="G188" s="23"/>
+      <c r="H188" s="23"/>
+      <c r="I188" s="23"/>
+      <c r="J188" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D122:J122"/>
-    <mergeCell ref="D123:J123"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D108:J108"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D117:J117"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D83:J83"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
+  <mergeCells count="103">
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D188:J188"/>
+    <mergeCell ref="D182:J182"/>
+    <mergeCell ref="D183:J183"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D168:J168"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D173:J173"/>
+    <mergeCell ref="D177:J177"/>
+    <mergeCell ref="D178:J178"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D167:J167"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
     <mergeCell ref="D127:J127"/>
     <mergeCell ref="D128:J128"/>
     <mergeCell ref="D132:J132"/>
@@ -5155,27 +5214,62 @@
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="D33:J33"/>
     <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D167:J167"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
-    <mergeCell ref="D182:J182"/>
-    <mergeCell ref="D183:J183"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D168:J168"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D173:J173"/>
-    <mergeCell ref="D177:J177"/>
-    <mergeCell ref="D178:J178"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D118:J118"/>
+    <mergeCell ref="D122:J122"/>
+    <mergeCell ref="D123:J123"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D113:J113"/>
+    <mergeCell ref="D117:J117"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5191,28 +5285,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
+      <c r="A1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="178">
   <si>
     <t>Name</t>
   </si>
@@ -312,9 +312,6 @@
     <t>Fragile, Infiltrating</t>
   </si>
   <si>
-    <t>Weakening</t>
-  </si>
-  <si>
     <t>New Mortarion's miniature in old one's style but with purple grape motiff</t>
   </si>
   <si>
@@ -366,9 +363,6 @@
     <t>Slippery, Vulnerable:Lightning, Resistant:Fire</t>
   </si>
   <si>
-    <t>Vulnerable:Fire, Is actually 3 goblins</t>
-  </si>
-  <si>
     <t>Vulnerable:Fire</t>
   </si>
   <si>
@@ -438,9 +432,6 @@
     <t>Crude mage</t>
   </si>
   <si>
-    <t>Water hazard but in oiled robes</t>
-  </si>
-  <si>
     <t>Oliokinesis</t>
   </si>
   <si>
@@ -471,12 +462,6 @@
     <t>Ice citadel</t>
   </si>
   <si>
-    <t>Miniature icewind citadel</t>
-  </si>
-  <si>
-    <t>Resistant:Frost, Immovable, Woundable, Freezing</t>
-  </si>
-  <si>
     <t>Galapo</t>
   </si>
   <si>
@@ -513,9 +498,6 @@
     <t>Pushing, Merging</t>
   </si>
   <si>
-    <t>Pushing, Merging, Evading</t>
-  </si>
-  <si>
     <t>Hazar</t>
   </si>
   <si>
@@ -540,13 +522,34 @@
     <t>Evading, Merging</t>
   </si>
   <si>
-    <t>Bladesinger</t>
-  </si>
-  <si>
     <t>Bladeguarded</t>
   </si>
   <si>
-    <t>Old drukhari baasic troop</t>
+    <t>Vulnerable:Fire, Is actually 3 goblins, Woundable</t>
+  </si>
+  <si>
+    <t>Weakening, Woundable</t>
+  </si>
+  <si>
+    <t>Old big eye SoB model</t>
+  </si>
+  <si>
+    <t>Disney Hercules ice titan</t>
+  </si>
+  <si>
+    <t>Resistant:Frost, Immovable, Freezing</t>
+  </si>
+  <si>
+    <t>Penetrating, Merging</t>
+  </si>
+  <si>
+    <t>Amphibian</t>
+  </si>
+  <si>
+    <t>Old drukhari basic troop</t>
+  </si>
+  <si>
+    <t>Blademaster</t>
   </si>
 </sst>
 </file>
@@ -758,16 +761,20 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
@@ -779,28 +786,24 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -1128,30 +1131,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1330,44 +1333,44 @@
     </row>
     <row r="7" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="36" t="s">
+      <c r="V7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
+      <c r="W7" s="26"/>
+      <c r="X7" s="26"/>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
     </row>
     <row r="8" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
@@ -1377,39 +1380,39 @@
       <c r="C8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="32"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="36" t="s">
+      <c r="V8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
+      <c r="W8" s="26"/>
+      <c r="X8" s="26"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="26"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
@@ -1506,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>8</v>
@@ -1567,46 +1570,46 @@
       <c r="C12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="36" t="s">
+      <c r="V12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
     </row>
     <row r="13" spans="1:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
@@ -1617,27 +1620,27 @@
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
+      <c r="V13" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O14"/>
@@ -1795,77 +1798,77 @@
       <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="36" t="s">
+      <c r="V17" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="36"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="36"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="26"/>
+      <c r="AA17" s="26"/>
+      <c r="AB17" s="26"/>
     </row>
     <row r="18" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="37" t="s">
+      <c r="M18" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="36" t="s">
+      <c r="V18" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
     </row>
     <row r="19" spans="3:28" ht="15" x14ac:dyDescent="0.25">
       <c r="O19"/>
@@ -1974,53 +1977,53 @@
       <c r="C22" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M22" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
+      <c r="M23" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
     </row>
     <row r="25" spans="3:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="15" t="s">
@@ -2126,46 +2129,46 @@
       <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="37"/>
-      <c r="S27" s="37"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
     </row>
     <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N28" s="23"/>
       <c r="O28" s="23"/>
@@ -2226,7 +2229,7 @@
     </row>
     <row r="31" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D31" s="15">
         <v>3</v>
@@ -2241,7 +2244,7 @@
         <v>7</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>8</v>
@@ -2278,53 +2281,53 @@
       <c r="C32" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30"/>
+      <c r="D32" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="32"/>
       <c r="L32" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="33"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="29"/>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C33" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="30"/>
+      <c r="D33" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="32"/>
       <c r="L33" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="33"/>
+      <c r="M33" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="29"/>
     </row>
     <row r="35" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C35" s="15" t="s">
@@ -2430,53 +2433,53 @@
       <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="30"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="32"/>
       <c r="L37" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="31" t="s">
+      <c r="M37" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="32"/>
-      <c r="R37" s="32"/>
-      <c r="S37" s="33"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="29"/>
     </row>
     <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="30"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="32"/>
       <c r="L38" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="33"/>
+      <c r="M38" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
     </row>
     <row r="40" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C40" s="7" t="s">
@@ -2594,15 +2597,15 @@
       <c r="L42" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="31" t="s">
+      <c r="M42" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
-      <c r="S42" s="33"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="29"/>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C43" s="7" t="s">
@@ -2620,15 +2623,15 @@
       <c r="L43" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="31" t="s">
+      <c r="M43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="32"/>
-      <c r="S43" s="33"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="29"/>
     </row>
     <row r="45" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="7" t="s">
@@ -2746,15 +2749,15 @@
       <c r="L47" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="31" t="s">
+      <c r="M47" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="33"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="29"/>
     </row>
     <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="7" t="s">
@@ -2772,15 +2775,15 @@
       <c r="L48" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="31" t="s">
+      <c r="M48" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="N48" s="32"/>
-      <c r="O48" s="32"/>
-      <c r="P48" s="32"/>
-      <c r="Q48" s="32"/>
-      <c r="R48" s="32"/>
-      <c r="S48" s="33"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="29"/>
     </row>
     <row r="50" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="7" t="s">
@@ -2834,7 +2837,7 @@
     </row>
     <row r="51" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C51" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51" s="7">
         <v>2</v>
@@ -2887,7 +2890,7 @@
         <v>11</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
@@ -2898,15 +2901,15 @@
       <c r="L52" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="34" t="s">
+      <c r="M52" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
     </row>
     <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="7" t="s">
@@ -2924,15 +2927,15 @@
       <c r="L53" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="34" t="s">
+      <c r="M53" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C55" s="7" t="s">
@@ -2962,7 +2965,7 @@
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C56" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D56" s="7">
         <v>1</v>
@@ -2991,7 +2994,7 @@
         <v>11</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="23"/>
@@ -3150,29 +3153,29 @@
       <c r="C67" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="26"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="38"/>
     </row>
     <row r="68" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="D68" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="26"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="38"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C70" s="15" t="s">
@@ -3230,29 +3233,29 @@
       <c r="C72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="27" t="s">
+      <c r="D72" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="33"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
     </row>
     <row r="73" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
+      <c r="D73" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E73" s="33"/>
+      <c r="F73" s="33"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="33"/>
+      <c r="J73" s="33"/>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C75" s="7" t="s">
@@ -3311,7 +3314,7 @@
         <v>11</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E77" s="23"/>
       <c r="F77" s="23"/>
@@ -3325,7 +3328,7 @@
         <v>17</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E78" s="23"/>
       <c r="F78" s="23"/>
@@ -3390,29 +3393,29 @@
       <c r="C82" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="24" t="s">
+      <c r="D82" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25"/>
-      <c r="J82" s="26"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+      <c r="J82" s="38"/>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C83" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="D83" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25"/>
-      <c r="J83" s="26"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="37"/>
+      <c r="J83" s="38"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C85" s="8" t="s">
@@ -3471,7 +3474,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
@@ -3485,7 +3488,7 @@
         <v>17</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
@@ -3522,7 +3525,7 @@
     </row>
     <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C91" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D91" s="9">
         <v>3</v>
@@ -3551,7 +3554,7 @@
         <v>11</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
@@ -3565,7 +3568,7 @@
         <v>17</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
@@ -3602,7 +3605,7 @@
     </row>
     <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D96" s="9">
         <v>7</v>
@@ -3631,7 +3634,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E97" s="23"/>
       <c r="F97" s="23"/>
@@ -3645,7 +3648,7 @@
         <v>17</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
@@ -3682,7 +3685,7 @@
     </row>
     <row r="101" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C101" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D101" s="9">
         <v>2</v>
@@ -3711,7 +3714,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
@@ -3725,7 +3728,7 @@
         <v>17</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23"/>
@@ -3762,7 +3765,7 @@
     </row>
     <row r="106" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C106" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D106" s="16">
         <v>3</v>
@@ -3791,7 +3794,7 @@
         <v>11</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="23"/>
@@ -3805,7 +3808,7 @@
         <v>17</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
@@ -3842,7 +3845,7 @@
     </row>
     <row r="111" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C111" s="16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D111" s="16">
         <v>3</v>
@@ -3871,7 +3874,7 @@
         <v>11</v>
       </c>
       <c r="D112" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
@@ -3885,7 +3888,7 @@
         <v>17</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="23"/>
@@ -3922,7 +3925,7 @@
     </row>
     <row r="116" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C116" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D116" s="16">
         <v>2</v>
@@ -3951,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="D117" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E117" s="23"/>
       <c r="F117" s="23"/>
@@ -3965,7 +3968,7 @@
         <v>17</v>
       </c>
       <c r="D118" s="23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
@@ -4002,7 +4005,7 @@
     </row>
     <row r="121" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C121" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D121" s="16">
         <v>12</v>
@@ -4031,7 +4034,7 @@
         <v>11</v>
       </c>
       <c r="D122" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
@@ -4045,7 +4048,7 @@
         <v>17</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E123" s="23"/>
       <c r="F123" s="23"/>
@@ -4082,7 +4085,7 @@
     </row>
     <row r="126" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C126" s="19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D126" s="19">
         <v>2</v>
@@ -4097,7 +4100,7 @@
         <v>10</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I126" s="19" t="s">
         <v>10</v>
@@ -4111,7 +4114,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="23" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E127" s="23"/>
       <c r="F127" s="23"/>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="131" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C131" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D131" s="19">
         <v>3</v>
@@ -4180,7 +4183,7 @@
         <v>37</v>
       </c>
       <c r="I131" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J131" s="19">
         <v>25</v>
@@ -4191,7 +4194,7 @@
         <v>11</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
@@ -4205,7 +4208,7 @@
         <v>17</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E133" s="23"/>
       <c r="F133" s="23"/>
@@ -4254,7 +4257,7 @@
     </row>
     <row r="136" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C136" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D136" s="19">
         <v>3</v>
@@ -4288,7 +4291,7 @@
         <v>11</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="E137" s="23"/>
       <c r="F137" s="23"/>
@@ -4307,7 +4310,7 @@
         <v>17</v>
       </c>
       <c r="D138" s="23" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
@@ -4361,7 +4364,7 @@
     </row>
     <row r="141" spans="3:17" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="19" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D141" s="19">
         <v>4</v>
@@ -4379,7 +4382,7 @@
         <v>8</v>
       </c>
       <c r="I141" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J141" s="19">
         <v>50</v>
@@ -4390,7 +4393,7 @@
         <v>11</v>
       </c>
       <c r="D142" s="23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
@@ -4404,7 +4407,7 @@
         <v>17</v>
       </c>
       <c r="D143" s="23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E143" s="23"/>
       <c r="F143" s="23"/>
@@ -4441,7 +4444,7 @@
     </row>
     <row r="146" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C146" s="19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D146" s="19">
         <v>4</v>
@@ -4470,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="D147" s="23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E147" s="23"/>
       <c r="F147" s="23"/>
@@ -4484,7 +4487,7 @@
         <v>17</v>
       </c>
       <c r="D148" s="23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
@@ -4521,7 +4524,7 @@
     </row>
     <row r="151" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C151" s="19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D151" s="19">
         <v>6</v>
@@ -4550,7 +4553,7 @@
         <v>11</v>
       </c>
       <c r="D152" s="23" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
@@ -4564,7 +4567,7 @@
         <v>17</v>
       </c>
       <c r="D153" s="23" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="E153" s="23"/>
       <c r="F153" s="23"/>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="156" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C156" s="20" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D156" s="20">
         <v>3</v>
@@ -4630,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="D157" s="23" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E157" s="23"/>
       <c r="F157" s="23"/>
@@ -4644,7 +4647,7 @@
         <v>17</v>
       </c>
       <c r="D158" s="23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
@@ -4681,7 +4684,7 @@
     </row>
     <row r="161" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C161" s="20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D161" s="20">
         <v>3</v>
@@ -4710,7 +4713,7 @@
         <v>11</v>
       </c>
       <c r="D162" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
@@ -4724,7 +4727,7 @@
         <v>17</v>
       </c>
       <c r="D163" s="23" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E163" s="23"/>
       <c r="F163" s="23"/>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="166" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C166" s="20" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D166" s="20">
         <v>3</v>
@@ -4806,7 +4809,7 @@
         <v>11</v>
       </c>
       <c r="D167" s="23" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E167" s="23"/>
       <c r="F167" s="23"/>
@@ -4815,20 +4818,20 @@
       <c r="I167" s="23"/>
       <c r="J167" s="23"/>
       <c r="L167"/>
-      <c r="M167" s="38"/>
-      <c r="N167" s="38"/>
-      <c r="O167" s="38"/>
-      <c r="P167" s="38"/>
-      <c r="Q167" s="38"/>
-      <c r="R167" s="38"/>
-      <c r="S167" s="38"/>
+      <c r="M167" s="24"/>
+      <c r="N167" s="24"/>
+      <c r="O167" s="24"/>
+      <c r="P167" s="24"/>
+      <c r="Q167" s="24"/>
+      <c r="R167" s="24"/>
+      <c r="S167" s="24"/>
     </row>
     <row r="168" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C168" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D168" s="23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E168" s="23"/>
       <c r="F168" s="23"/>
@@ -4837,13 +4840,13 @@
       <c r="I168" s="23"/>
       <c r="J168" s="23"/>
       <c r="L168"/>
-      <c r="M168" s="38"/>
-      <c r="N168" s="38"/>
-      <c r="O168" s="38"/>
-      <c r="P168" s="38"/>
-      <c r="Q168" s="38"/>
-      <c r="R168" s="38"/>
-      <c r="S168" s="38"/>
+      <c r="M168" s="24"/>
+      <c r="N168" s="24"/>
+      <c r="O168" s="24"/>
+      <c r="P168" s="24"/>
+      <c r="Q168" s="24"/>
+      <c r="R168" s="24"/>
+      <c r="S168" s="24"/>
     </row>
     <row r="170" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C170" s="20" t="s">
@@ -4873,7 +4876,7 @@
     </row>
     <row r="171" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C171" s="20" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D171" s="20">
         <v>4</v>
@@ -4902,7 +4905,7 @@
         <v>11</v>
       </c>
       <c r="D172" s="23" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E172" s="23"/>
       <c r="F172" s="23"/>
@@ -4916,7 +4919,7 @@
         <v>17</v>
       </c>
       <c r="D173" s="23" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E173" s="23"/>
       <c r="F173" s="23"/>
@@ -4953,7 +4956,7 @@
     </row>
     <row r="176" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C176" s="20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D176" s="20">
         <v>3</v>
@@ -4982,7 +4985,7 @@
         <v>11</v>
       </c>
       <c r="D177" s="23" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E177" s="23"/>
       <c r="F177" s="23"/>
@@ -4996,7 +4999,7 @@
         <v>17</v>
       </c>
       <c r="D178" s="23" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E178" s="23"/>
       <c r="F178" s="23"/>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="181" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C181" s="21" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D181" s="21">
         <v>3</v>
@@ -5062,7 +5065,7 @@
         <v>11</v>
       </c>
       <c r="D182" s="23" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E182" s="23"/>
       <c r="F182" s="23"/>
@@ -5076,7 +5079,7 @@
         <v>17</v>
       </c>
       <c r="D183" s="23" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E183" s="23"/>
       <c r="F183" s="23"/>
@@ -5113,7 +5116,7 @@
     </row>
     <row r="186" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C186" s="22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D186" s="22">
         <v>3</v>
@@ -5156,7 +5159,7 @@
         <v>17</v>
       </c>
       <c r="D188" s="23" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E188" s="23"/>
       <c r="F188" s="23"/>
@@ -5167,29 +5170,62 @@
     </row>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="D187:J187"/>
-    <mergeCell ref="D188:J188"/>
-    <mergeCell ref="D182:J182"/>
-    <mergeCell ref="D183:J183"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D168:J168"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D173:J173"/>
-    <mergeCell ref="D177:J177"/>
-    <mergeCell ref="D178:J178"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D167:J167"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D118:J118"/>
+    <mergeCell ref="D122:J122"/>
+    <mergeCell ref="D123:J123"/>
+    <mergeCell ref="D107:J107"/>
+    <mergeCell ref="D108:J108"/>
+    <mergeCell ref="D112:J112"/>
+    <mergeCell ref="D113:J113"/>
+    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="D68:J68"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
     <mergeCell ref="D127:J127"/>
     <mergeCell ref="D128:J128"/>
     <mergeCell ref="D132:J132"/>
@@ -5214,62 +5250,29 @@
     <mergeCell ref="M28:S28"/>
     <mergeCell ref="D33:J33"/>
     <mergeCell ref="D37:J37"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D83:J83"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
-    <mergeCell ref="D118:J118"/>
-    <mergeCell ref="D122:J122"/>
-    <mergeCell ref="D123:J123"/>
-    <mergeCell ref="D107:J107"/>
-    <mergeCell ref="D108:J108"/>
-    <mergeCell ref="D112:J112"/>
-    <mergeCell ref="D113:J113"/>
-    <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D167:J167"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D187:J187"/>
+    <mergeCell ref="D188:J188"/>
+    <mergeCell ref="D182:J182"/>
+    <mergeCell ref="D183:J183"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D168:J168"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D173:J173"/>
+    <mergeCell ref="D177:J177"/>
+    <mergeCell ref="D178:J178"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5285,28 +5288,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="35"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -426,9 +426,6 @@
     <t>Triton or Poseidon</t>
   </si>
   <si>
-    <t>Hydrokinesis</t>
-  </si>
-  <si>
     <t>Crude mage</t>
   </si>
   <si>
@@ -550,6 +547,9 @@
   </si>
   <si>
     <t>Resistant:Physical, Immovable, Woundable, Penetrating, Infiltrating</t>
+  </si>
+  <si>
+    <t>Dripping, Hydrokinesis</t>
   </si>
 </sst>
 </file>
@@ -753,10 +753,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -766,10 +762,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -781,21 +783,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -1124,30 +1124,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
     </row>
     <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
@@ -1174,28 +1174,28 @@
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="21" t="s">
+      <c r="D5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="21" t="s">
+      <c r="G5" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="20" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1251,29 +1251,29 @@
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="21">
-        <v>2</v>
-      </c>
-      <c r="E6" s="21">
-        <v>1</v>
-      </c>
-      <c r="F6" s="21" t="s">
+      <c r="C6" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="20">
+        <v>5</v>
+      </c>
+      <c r="E6" s="20">
+        <v>2</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="21">
-        <v>30</v>
+      <c r="G6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="20">
+        <v>80</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>27</v>
@@ -1328,84 +1328,84 @@
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
+      <c r="D7" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="27"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V7" s="28" t="s">
+      <c r="V7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="D8" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="27"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="28" t="s">
+      <c r="V8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="34"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="O9"/>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D11" s="13">
         <v>3</v>
@@ -1563,77 +1563,77 @@
       <c r="C12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
+      <c r="D12" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V12" s="28" t="s">
+      <c r="V12" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="W12" s="28"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="34"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="D13" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="M13" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="28" t="s">
+      <c r="V13" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
+      <c r="W13" s="34"/>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="34"/>
     </row>
     <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14"/>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="C16" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
@@ -1791,77 +1791,77 @@
       <c r="C17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
+      <c r="D17" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="V17" s="28" t="s">
+      <c r="V17" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="W17" s="28"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="34"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C18" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
+      <c r="D18" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="27" t="s">
+      <c r="M18" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V18" s="28" t="s">
+      <c r="V18" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="28"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="34"/>
     </row>
     <row r="19" spans="3:28" x14ac:dyDescent="0.25">
       <c r="C19" s="18"/>
@@ -1978,53 +1978,53 @@
       <c r="C22" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="34"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="27" t="s">
+      <c r="M22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
     </row>
     <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="34"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="27"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="27" t="s">
+      <c r="M23" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
     </row>
     <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="17" t="s">
@@ -2130,77 +2130,77 @@
       <c r="C27" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="27"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="27" t="s">
+      <c r="M27" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
     </row>
     <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="34"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="27"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="22" t="s">
+      <c r="M28" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
     </row>
     <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="21" t="s">
+      <c r="D30" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="I30" s="21" t="s">
+      <c r="G30" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="21" t="s">
+      <c r="J30" s="20" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="11" t="s">
@@ -2229,29 +2229,29 @@
       </c>
     </row>
     <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="21">
-        <v>3</v>
-      </c>
-      <c r="E31" s="21">
-        <v>1</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="21" t="s">
+      <c r="C31" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="20">
+        <v>3</v>
+      </c>
+      <c r="E31" s="20">
+        <v>1</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="21">
-        <v>30</v>
+      <c r="H31" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="20">
+        <v>25</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>45</v>
@@ -2279,18 +2279,18 @@
       </c>
     </row>
     <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="31"/>
+      <c r="D32" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="27"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
@@ -2305,18 +2305,18 @@
       <c r="S32" s="31"/>
     </row>
     <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="31"/>
+      <c r="D33" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="27"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
@@ -2434,15 +2434,15 @@
       <c r="C37" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="34"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="27"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
@@ -2460,27 +2460,27 @@
       <c r="C38" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="34"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="27"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="22"/>
+      <c r="M38" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
     </row>
     <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="15" t="s">
@@ -2586,15 +2586,15 @@
       <c r="C42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="26"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="24"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
@@ -2612,15 +2612,15 @@
       <c r="C43" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="26"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="24"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
@@ -2738,15 +2738,15 @@
       <c r="C47" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="34"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="27"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
@@ -2764,15 +2764,15 @@
       <c r="C48" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="34"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="27"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
@@ -2890,53 +2890,53 @@
       <c r="C52" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="33"/>
-      <c r="J52" s="34"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="27"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="36" t="s">
+      <c r="M52" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="36"/>
-      <c r="O52" s="36"/>
-      <c r="P52" s="36"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="36"/>
-      <c r="S52" s="36"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
     </row>
     <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="32" t="s">
+      <c r="D53" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="34"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="27"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="36" t="s">
+      <c r="M53" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="36"/>
-      <c r="S53" s="36"/>
+      <c r="N53" s="28"/>
+      <c r="O53" s="28"/>
+      <c r="P53" s="28"/>
+      <c r="Q53" s="28"/>
+      <c r="R53" s="28"/>
+      <c r="S53" s="28"/>
     </row>
     <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
       <c r="C55" s="20" t="s">
@@ -3042,15 +3042,15 @@
       <c r="C57" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="34"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="27"/>
       <c r="L57" s="19" t="s">
         <v>11</v>
       </c>
@@ -3068,15 +3068,15 @@
       <c r="C58" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
-      <c r="J58" s="34"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="27"/>
       <c r="L58" s="19" t="s">
         <v>17</v>
       </c>
@@ -3194,55 +3194,55 @@
       <c r="C62" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="34"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="27"/>
       <c r="L62" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="36" t="s">
+      <c r="M62" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="N62" s="36"/>
-      <c r="O62" s="36"/>
-      <c r="P62" s="36"/>
-      <c r="Q62" s="36"/>
-      <c r="R62" s="36"/>
-      <c r="S62" s="36"/>
+      <c r="N62" s="28"/>
+      <c r="O62" s="28"/>
+      <c r="P62" s="28"/>
+      <c r="Q62" s="28"/>
+      <c r="R62" s="28"/>
+      <c r="S62" s="28"/>
     </row>
     <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="34"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="27"/>
       <c r="L63" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="36" t="s">
+      <c r="M63" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="N63" s="36"/>
-      <c r="O63" s="36"/>
-      <c r="P63" s="36"/>
-      <c r="Q63" s="36"/>
-      <c r="R63" s="36"/>
-      <c r="S63" s="36"/>
-    </row>
-    <row r="65" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="28"/>
+    </row>
+    <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="15" t="s">
         <v>0</v>
       </c>
@@ -3267,8 +3267,32 @@
       <c r="J65" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L65" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M65" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N65" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O65" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P65" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q65" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R65" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S65" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="15" t="s">
         <v>85</v>
       </c>
@@ -3293,36 +3317,84 @@
       <c r="J66" s="15">
         <v>40</v>
       </c>
-    </row>
-    <row r="67" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L66" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M66" s="21">
+        <v>3</v>
+      </c>
+      <c r="N66" s="21">
+        <v>1</v>
+      </c>
+      <c r="O66" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P66" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q66" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="R66" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S66" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-      <c r="J67" s="26"/>
-    </row>
-    <row r="68" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="24"/>
+      <c r="L67" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M67" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="31"/>
+    </row>
+    <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="D68" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="26"/>
-    </row>
-    <row r="70" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="24"/>
+      <c r="L68" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="M68" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="N68" s="30"/>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="30"/>
+      <c r="R68" s="30"/>
+      <c r="S68" s="31"/>
+    </row>
+    <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="17" t="s">
         <v>0</v>
       </c>
@@ -3347,8 +3419,32 @@
       <c r="J70" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="71" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L70" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="M70" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N70" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O70" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P70" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="R70" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="S70" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="17" t="s">
         <v>88</v>
       </c>
@@ -3368,41 +3464,89 @@
         <v>0</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J71" s="17">
         <v>50</v>
       </c>
-    </row>
-    <row r="72" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L71" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="M71" s="21">
+        <v>2</v>
+      </c>
+      <c r="N71" s="21">
+        <v>1</v>
+      </c>
+      <c r="O71" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P71" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q71" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="R71" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S71" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="34"/>
-    </row>
-    <row r="73" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="27"/>
+      <c r="L72" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M72" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
+      <c r="R72" s="30"/>
+      <c r="S72" s="31"/>
+    </row>
+    <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" s="33"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="34"/>
-    </row>
-    <row r="75" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D73" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="27"/>
+      <c r="L73" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="M73" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="N73" s="28"/>
+      <c r="O73" s="28"/>
+      <c r="P73" s="28"/>
+      <c r="Q73" s="28"/>
+      <c r="R73" s="28"/>
+      <c r="S73" s="28"/>
+    </row>
+    <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="15" t="s">
         <v>0</v>
       </c>
@@ -3428,7 +3572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="15" t="s">
         <v>90</v>
       </c>
@@ -3454,35 +3598,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="25"/>
-      <c r="J77" s="26"/>
-    </row>
-    <row r="78" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="24"/>
+    </row>
+    <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
-      <c r="J78" s="26"/>
-    </row>
-    <row r="80" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="24"/>
+    </row>
+    <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="15" t="s">
         <v>0</v>
       </c>
@@ -3538,110 +3682,34 @@
       <c r="C82" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="24" t="s">
+      <c r="D82" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25"/>
-      <c r="J82" s="26"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="23"/>
+      <c r="G82" s="23"/>
+      <c r="H82" s="23"/>
+      <c r="I82" s="23"/>
+      <c r="J82" s="24"/>
     </row>
     <row r="83" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="D83" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25"/>
-      <c r="J83" s="26"/>
-    </row>
-    <row r="85" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I85" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J85" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="15">
-        <v>5</v>
-      </c>
-      <c r="E86" s="15">
-        <v>2</v>
-      </c>
-      <c r="F86" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G86" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H86" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I86" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J86" s="15">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
-      <c r="I87" s="25"/>
-      <c r="J87" s="26"/>
-    </row>
-    <row r="88" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="25"/>
-      <c r="J88" s="26"/>
-    </row>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="23"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="24"/>
+    </row>
+    <row r="85" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="15" t="s">
         <v>0</v>
@@ -3698,29 +3766,29 @@
       <c r="C92" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="24" t="s">
+      <c r="D92" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="25"/>
-      <c r="J92" s="26"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="23"/>
+      <c r="J92" s="24"/>
     </row>
     <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="D93" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="25"/>
-      <c r="J93" s="26"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="24"/>
     </row>
     <row r="95" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="15" t="s">
@@ -3778,29 +3846,29 @@
       <c r="C97" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="25"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="25"/>
-      <c r="J97" s="26"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="24"/>
     </row>
     <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="24" t="s">
+      <c r="D98" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
-      <c r="J98" s="26"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="24"/>
     </row>
     <row r="100" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="15" t="s">
@@ -3858,29 +3926,29 @@
       <c r="C102" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="24" t="s">
+      <c r="D102" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
-      <c r="I102" s="25"/>
-      <c r="J102" s="26"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="24"/>
     </row>
     <row r="103" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="24" t="s">
+      <c r="D103" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
-      <c r="I103" s="25"/>
-      <c r="J103" s="26"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+      <c r="G103" s="23"/>
+      <c r="H103" s="23"/>
+      <c r="I103" s="23"/>
+      <c r="J103" s="24"/>
     </row>
     <row r="105" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="15" t="s">
@@ -3938,29 +4006,29 @@
       <c r="C107" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="24" t="s">
+      <c r="D107" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="25"/>
-      <c r="J107" s="26"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="24"/>
     </row>
     <row r="108" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="24" t="s">
+      <c r="D108" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25"/>
-      <c r="J108" s="26"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="24"/>
     </row>
     <row r="110" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="15" t="s">
@@ -4018,29 +4086,29 @@
       <c r="C112" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
-      <c r="I112" s="25"/>
-      <c r="J112" s="26"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="24"/>
     </row>
     <row r="113" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-      <c r="H113" s="25"/>
-      <c r="I113" s="25"/>
-      <c r="J113" s="26"/>
+      <c r="E113" s="23"/>
+      <c r="F113" s="23"/>
+      <c r="G113" s="23"/>
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+      <c r="J113" s="24"/>
     </row>
     <row r="115" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="15" t="s">
@@ -4098,29 +4166,29 @@
       <c r="C117" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="24" t="s">
+      <c r="D117" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E117" s="25"/>
-      <c r="F117" s="25"/>
-      <c r="G117" s="25"/>
-      <c r="H117" s="25"/>
-      <c r="I117" s="25"/>
-      <c r="J117" s="26"/>
+      <c r="E117" s="23"/>
+      <c r="F117" s="23"/>
+      <c r="G117" s="23"/>
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
+      <c r="J117" s="24"/>
     </row>
     <row r="118" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E118" s="25"/>
-      <c r="F118" s="25"/>
-      <c r="G118" s="25"/>
-      <c r="H118" s="25"/>
-      <c r="I118" s="25"/>
-      <c r="J118" s="26"/>
+      <c r="E118" s="23"/>
+      <c r="F118" s="23"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="24"/>
     </row>
     <row r="120" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="15" t="s">
@@ -4178,29 +4246,29 @@
       <c r="C122" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="24" t="s">
+      <c r="D122" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="25"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="25"/>
-      <c r="H122" s="25"/>
-      <c r="I122" s="25"/>
-      <c r="J122" s="26"/>
+      <c r="E122" s="23"/>
+      <c r="F122" s="23"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="23"/>
+      <c r="I122" s="23"/>
+      <c r="J122" s="24"/>
     </row>
     <row r="123" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="24" t="s">
+      <c r="D123" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25"/>
-      <c r="G123" s="25"/>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="26"/>
+      <c r="E123" s="23"/>
+      <c r="F123" s="23"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="24"/>
     </row>
     <row r="125" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="15" t="s">
@@ -4258,110 +4326,34 @@
       <c r="C127" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="E127" s="25"/>
-      <c r="F127" s="25"/>
-      <c r="G127" s="25"/>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25"/>
-      <c r="J127" s="26"/>
+      <c r="D127" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="24"/>
     </row>
     <row r="128" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="24" t="s">
+      <c r="D128" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="25"/>
-      <c r="I128" s="25"/>
-      <c r="J128" s="26"/>
-    </row>
-    <row r="130" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E130" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F130" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G130" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H130" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I130" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J130" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="131" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C131" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D131" s="15">
-        <v>3</v>
-      </c>
-      <c r="E131" s="15">
-        <v>1</v>
-      </c>
-      <c r="F131" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G131" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H131" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I131" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="J131" s="15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C132" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="25"/>
-      <c r="H132" s="25"/>
-      <c r="I132" s="25"/>
-      <c r="J132" s="26"/>
-    </row>
-    <row r="133" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C133" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D133" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E133" s="25"/>
-      <c r="F133" s="25"/>
-      <c r="G133" s="25"/>
-      <c r="H133" s="25"/>
-      <c r="I133" s="25"/>
-      <c r="J133" s="26"/>
-    </row>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="24"/>
+    </row>
+    <row r="130" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="18"/>
       <c r="D134" s="18"/>
@@ -4410,7 +4402,7 @@
     </row>
     <row r="136" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D136" s="15">
         <v>3</v>
@@ -4443,15 +4435,15 @@
       <c r="C137" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="25"/>
-      <c r="H137" s="25"/>
-      <c r="I137" s="25"/>
-      <c r="J137" s="26"/>
+      <c r="D137" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="24"/>
       <c r="M137"/>
       <c r="N137"/>
       <c r="O137"/>
@@ -4462,15 +4454,15 @@
       <c r="C138" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="25"/>
-      <c r="H138" s="25"/>
-      <c r="I138" s="25"/>
-      <c r="J138" s="26"/>
+      <c r="D138" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E138" s="23"/>
+      <c r="F138" s="23"/>
+      <c r="G138" s="23"/>
+      <c r="H138" s="23"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="24"/>
       <c r="M138"/>
       <c r="N138"/>
       <c r="O138"/>
@@ -4525,7 +4517,7 @@
     </row>
     <row r="141" spans="3:17" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D141" s="15">
         <v>4</v>
@@ -4543,7 +4535,7 @@
         <v>8</v>
       </c>
       <c r="I141" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J141" s="15">
         <v>50</v>
@@ -4553,29 +4545,29 @@
       <c r="C142" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D142" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E142" s="25"/>
-      <c r="F142" s="25"/>
-      <c r="G142" s="25"/>
-      <c r="H142" s="25"/>
-      <c r="I142" s="25"/>
-      <c r="J142" s="26"/>
+      <c r="D142" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E142" s="23"/>
+      <c r="F142" s="23"/>
+      <c r="G142" s="23"/>
+      <c r="H142" s="23"/>
+      <c r="I142" s="23"/>
+      <c r="J142" s="24"/>
     </row>
     <row r="143" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C143" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25"/>
-      <c r="G143" s="25"/>
-      <c r="H143" s="25"/>
-      <c r="I143" s="25"/>
-      <c r="J143" s="26"/>
+      <c r="D143" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E143" s="23"/>
+      <c r="F143" s="23"/>
+      <c r="G143" s="23"/>
+      <c r="H143" s="23"/>
+      <c r="I143" s="23"/>
+      <c r="J143" s="24"/>
     </row>
     <row r="145" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C145" s="15" t="s">
@@ -4605,7 +4597,7 @@
     </row>
     <row r="146" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D146" s="15">
         <v>4</v>
@@ -4633,29 +4625,29 @@
       <c r="C147" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D147" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E147" s="25"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="25"/>
-      <c r="H147" s="25"/>
-      <c r="I147" s="25"/>
-      <c r="J147" s="26"/>
+      <c r="D147" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E147" s="23"/>
+      <c r="F147" s="23"/>
+      <c r="G147" s="23"/>
+      <c r="H147" s="23"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="24"/>
     </row>
     <row r="148" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D148" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
-      <c r="I148" s="25"/>
-      <c r="J148" s="26"/>
+      <c r="D148" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E148" s="23"/>
+      <c r="F148" s="23"/>
+      <c r="G148" s="23"/>
+      <c r="H148" s="23"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="24"/>
     </row>
     <row r="150" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C150" s="15" t="s">
@@ -4685,7 +4677,7 @@
     </row>
     <row r="151" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C151" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D151" s="15">
         <v>6</v>
@@ -4713,29 +4705,29 @@
       <c r="C152" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D152" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E152" s="25"/>
-      <c r="F152" s="25"/>
-      <c r="G152" s="25"/>
-      <c r="H152" s="25"/>
-      <c r="I152" s="25"/>
-      <c r="J152" s="26"/>
+      <c r="D152" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="E152" s="23"/>
+      <c r="F152" s="23"/>
+      <c r="G152" s="23"/>
+      <c r="H152" s="23"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="24"/>
     </row>
     <row r="153" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C153" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D153" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="25"/>
-      <c r="H153" s="25"/>
-      <c r="I153" s="25"/>
-      <c r="J153" s="26"/>
+      <c r="D153" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E153" s="23"/>
+      <c r="F153" s="23"/>
+      <c r="G153" s="23"/>
+      <c r="H153" s="23"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="24"/>
     </row>
     <row r="155" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C155" s="15" t="s">
@@ -4765,7 +4757,7 @@
     </row>
     <row r="156" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C156" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D156" s="15">
         <v>3</v>
@@ -4793,29 +4785,29 @@
       <c r="C157" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D157" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="26"/>
+      <c r="D157" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="E157" s="23"/>
+      <c r="F157" s="23"/>
+      <c r="G157" s="23"/>
+      <c r="H157" s="23"/>
+      <c r="I157" s="23"/>
+      <c r="J157" s="24"/>
     </row>
     <row r="158" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C158" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D158" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="E158" s="25"/>
-      <c r="F158" s="25"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
-      <c r="I158" s="25"/>
-      <c r="J158" s="26"/>
+      <c r="D158" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="E158" s="23"/>
+      <c r="F158" s="23"/>
+      <c r="G158" s="23"/>
+      <c r="H158" s="23"/>
+      <c r="I158" s="23"/>
+      <c r="J158" s="24"/>
     </row>
     <row r="160" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C160" s="15" t="s">
@@ -4845,7 +4837,7 @@
     </row>
     <row r="161" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C161" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D161" s="15">
         <v>3</v>
@@ -4873,29 +4865,29 @@
       <c r="C162" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D162" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E162" s="25"/>
-      <c r="F162" s="25"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="25"/>
-      <c r="I162" s="25"/>
-      <c r="J162" s="26"/>
+      <c r="D162" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="E162" s="23"/>
+      <c r="F162" s="23"/>
+      <c r="G162" s="23"/>
+      <c r="H162" s="23"/>
+      <c r="I162" s="23"/>
+      <c r="J162" s="24"/>
     </row>
     <row r="163" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C163" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D163" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="E163" s="25"/>
-      <c r="F163" s="25"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="25"/>
-      <c r="I163" s="25"/>
-      <c r="J163" s="26"/>
+      <c r="D163" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="E163" s="23"/>
+      <c r="F163" s="23"/>
+      <c r="G163" s="23"/>
+      <c r="H163" s="23"/>
+      <c r="I163" s="23"/>
+      <c r="J163" s="24"/>
     </row>
     <row r="165" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C165" s="15" t="s">
@@ -4933,7 +4925,7 @@
     </row>
     <row r="166" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C166" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D166" s="15">
         <v>3</v>
@@ -4969,45 +4961,45 @@
       <c r="C167" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D167" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
-      <c r="I167" s="25"/>
-      <c r="J167" s="26"/>
+      <c r="D167" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="E167" s="23"/>
+      <c r="F167" s="23"/>
+      <c r="G167" s="23"/>
+      <c r="H167" s="23"/>
+      <c r="I167" s="23"/>
+      <c r="J167" s="24"/>
       <c r="L167"/>
-      <c r="M167" s="23"/>
-      <c r="N167" s="23"/>
-      <c r="O167" s="23"/>
-      <c r="P167" s="23"/>
-      <c r="Q167" s="23"/>
-      <c r="R167" s="23"/>
-      <c r="S167" s="23"/>
+      <c r="M167" s="36"/>
+      <c r="N167" s="36"/>
+      <c r="O167" s="36"/>
+      <c r="P167" s="36"/>
+      <c r="Q167" s="36"/>
+      <c r="R167" s="36"/>
+      <c r="S167" s="36"/>
     </row>
     <row r="168" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C168" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D168" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E168" s="25"/>
-      <c r="F168" s="25"/>
-      <c r="G168" s="25"/>
-      <c r="H168" s="25"/>
-      <c r="I168" s="25"/>
-      <c r="J168" s="26"/>
+      <c r="D168" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E168" s="23"/>
+      <c r="F168" s="23"/>
+      <c r="G168" s="23"/>
+      <c r="H168" s="23"/>
+      <c r="I168" s="23"/>
+      <c r="J168" s="24"/>
       <c r="L168"/>
-      <c r="M168" s="23"/>
-      <c r="N168" s="23"/>
-      <c r="O168" s="23"/>
-      <c r="P168" s="23"/>
-      <c r="Q168" s="23"/>
-      <c r="R168" s="23"/>
-      <c r="S168" s="23"/>
+      <c r="M168" s="36"/>
+      <c r="N168" s="36"/>
+      <c r="O168" s="36"/>
+      <c r="P168" s="36"/>
+      <c r="Q168" s="36"/>
+      <c r="R168" s="36"/>
+      <c r="S168" s="36"/>
     </row>
     <row r="170" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C170" s="15" t="s">
@@ -5037,7 +5029,7 @@
     </row>
     <row r="171" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C171" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D171" s="15">
         <v>4</v>
@@ -5065,29 +5057,29 @@
       <c r="C172" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D172" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="25"/>
-      <c r="H172" s="25"/>
-      <c r="I172" s="25"/>
-      <c r="J172" s="26"/>
+      <c r="D172" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E172" s="23"/>
+      <c r="F172" s="23"/>
+      <c r="G172" s="23"/>
+      <c r="H172" s="23"/>
+      <c r="I172" s="23"/>
+      <c r="J172" s="24"/>
     </row>
     <row r="173" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C173" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D173" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="E173" s="25"/>
-      <c r="F173" s="25"/>
-      <c r="G173" s="25"/>
-      <c r="H173" s="25"/>
-      <c r="I173" s="25"/>
-      <c r="J173" s="26"/>
+      <c r="D173" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" s="23"/>
+      <c r="F173" s="23"/>
+      <c r="G173" s="23"/>
+      <c r="H173" s="23"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="24"/>
     </row>
     <row r="175" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C175" s="15" t="s">
@@ -5117,7 +5109,7 @@
     </row>
     <row r="176" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C176" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D176" s="15">
         <v>3</v>
@@ -5145,32 +5137,113 @@
       <c r="C177" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D177" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="25"/>
-      <c r="H177" s="25"/>
-      <c r="I177" s="25"/>
-      <c r="J177" s="26"/>
+      <c r="D177" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E177" s="23"/>
+      <c r="F177" s="23"/>
+      <c r="G177" s="23"/>
+      <c r="H177" s="23"/>
+      <c r="I177" s="23"/>
+      <c r="J177" s="24"/>
     </row>
     <row r="178" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C178" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E178" s="25"/>
-      <c r="F178" s="25"/>
-      <c r="G178" s="25"/>
-      <c r="H178" s="25"/>
-      <c r="I178" s="25"/>
-      <c r="J178" s="26"/>
+      <c r="D178" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E178" s="23"/>
+      <c r="F178" s="23"/>
+      <c r="G178" s="23"/>
+      <c r="H178" s="23"/>
+      <c r="I178" s="23"/>
+      <c r="J178" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="M67:S67"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D168:J168"/>
+    <mergeCell ref="D172:J172"/>
+    <mergeCell ref="D173:J173"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D142:J142"/>
+    <mergeCell ref="D143:J143"/>
+    <mergeCell ref="D147:J147"/>
+    <mergeCell ref="D148:J148"/>
+    <mergeCell ref="D177:J177"/>
+    <mergeCell ref="D178:J178"/>
+    <mergeCell ref="D157:J157"/>
+    <mergeCell ref="D158:J158"/>
+    <mergeCell ref="D162:J162"/>
+    <mergeCell ref="D163:J163"/>
+    <mergeCell ref="D167:J167"/>
+    <mergeCell ref="D152:J152"/>
+    <mergeCell ref="D153:J153"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="M27:S27"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="M62:S62"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="M63:S63"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="M57:S57"/>
+    <mergeCell ref="M58:S58"/>
     <mergeCell ref="D118:J118"/>
     <mergeCell ref="D122:J122"/>
     <mergeCell ref="D123:J123"/>
@@ -5193,87 +5266,6 @@
     <mergeCell ref="D97:J97"/>
     <mergeCell ref="D98:J98"/>
     <mergeCell ref="D102:J102"/>
-    <mergeCell ref="M63:S63"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="M57:S57"/>
-    <mergeCell ref="M58:S58"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="M62:S62"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="V17:AB17"/>
-    <mergeCell ref="V18:AB18"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="M32:S32"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="D177:J177"/>
-    <mergeCell ref="D178:J178"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D167:J167"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D168:J168"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D173:J173"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D132:J132"/>
-    <mergeCell ref="D133:J133"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="D87:J87"/>
-    <mergeCell ref="D88:J88"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5289,28 +5281,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="A1" s="33"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>

--- a/Units.xlsx
+++ b/Units.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -456,9 +456,6 @@
     <t>Charging</t>
   </si>
   <si>
-    <t>Ice citadel</t>
-  </si>
-  <si>
     <t>Galapo</t>
   </si>
   <si>
@@ -528,12 +525,6 @@
     <t>Old big eye SoB model</t>
   </si>
   <si>
-    <t>Disney Hercules ice titan</t>
-  </si>
-  <si>
-    <t>Resistant:Frost, Immovable, Freezing</t>
-  </si>
-  <si>
     <t>Penetrating, Merging</t>
   </si>
   <si>
@@ -550,6 +541,15 @@
   </si>
   <si>
     <t>Dripping, Hydrokinesis</t>
+  </si>
+  <si>
+    <t>Frosting giant</t>
+  </si>
+  <si>
+    <t>Disney Hercules ice titan made out of frosting</t>
+  </si>
+  <si>
+    <t>Resistant:Frost, Slowed, Freezing</t>
   </si>
 </sst>
 </file>
@@ -690,7 +690,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -753,6 +753,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -771,7 +774,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
@@ -783,19 +786,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -1102,54 +1105,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB178"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="1"/>
-    <col min="12" max="12" width="20.28515625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" style="1"/>
-    <col min="17" max="17" width="14.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="20.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="1"/>
+    <col min="15" max="15" width="10.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-    </row>
-    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-    </row>
-    <row r="3" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1160,7 +1163,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:28" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -1170,32 +1173,32 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="20" t="s">
+      <c r="D5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="20" t="s">
+      <c r="G5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="13" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1247,33 +1250,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="20">
-        <v>5</v>
-      </c>
-      <c r="E6" s="20">
-        <v>2</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="20">
-        <v>80</v>
+      <c r="C6" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="13">
+        <v>3</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="13">
+        <v>40</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>27</v>
@@ -1324,34 +1327,34 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="27"/>
+      <c r="D7" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
       <c r="L7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
       <c r="U7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1365,35 +1368,35 @@
       <c r="AA7" s="34"/>
       <c r="AB7" s="34"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="27"/>
+      <c r="D8" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
       <c r="L8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
       <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1407,33 +1410,33 @@
       <c r="AA8" s="34"/>
       <c r="AB8" s="34"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="O9"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C10" s="13" t="s">
+    <row r="10" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="D10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="13" t="s">
+      <c r="G10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="14" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="6" t="s">
@@ -1485,29 +1488,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="13">
-        <v>3</v>
-      </c>
-      <c r="E11" s="13">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="13" t="s">
+    <row r="11" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="14">
+        <v>3</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="H11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="14">
         <v>40</v>
       </c>
       <c r="L11" s="6" t="s">
@@ -1559,31 +1562,31 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C12" s="13" t="s">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
+      <c r="D12" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
       <c r="L12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="35" t="s">
+      <c r="M12" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
       <c r="U12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1597,31 +1600,31 @@
       <c r="AA12" s="34"/>
       <c r="AB12" s="34"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="C13" s="13" t="s">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="C13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
+      <c r="D13" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
       <c r="L13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="35" t="s">
+      <c r="M13" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
       <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1635,33 +1638,33 @@
       <c r="AA13" s="34"/>
       <c r="AB13" s="34"/>
     </row>
-    <row r="14" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O14"/>
       <c r="X14"/>
     </row>
-    <row r="15" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C15" s="14" t="s">
+    <row r="15" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C15" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="14" t="s">
+      <c r="D15" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14" t="s">
+      <c r="G15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="6" t="s">
@@ -1713,30 +1716,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="C16" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>1</v>
-      </c>
-      <c r="F16" s="14" t="s">
+    <row r="16" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C16" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="15">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="14">
-        <v>40</v>
+      <c r="H16" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="15">
+        <v>50</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>33</v>
@@ -1787,31 +1790,31 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C17" s="14" t="s">
+    <row r="17" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
+      <c r="D17" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="25"/>
       <c r="L17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="35" t="s">
+      <c r="M17" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
       <c r="U17" s="2" t="s">
         <v>11</v>
       </c>
@@ -1825,31 +1828,31 @@
       <c r="AA17" s="34"/>
       <c r="AB17" s="34"/>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
-      <c r="C18" s="14" t="s">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="D18" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="25"/>
       <c r="L18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="35" t="s">
+      <c r="M18" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
       <c r="U18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1863,7 +1866,7 @@
       <c r="AA18" s="34"/>
       <c r="AB18" s="34"/>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
@@ -1924,7 +1927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="17" t="s">
         <v>68</v>
       </c>
@@ -1974,81 +1977,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28"/>
       <c r="L22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="35" t="s">
+      <c r="M22" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-    </row>
-    <row r="23" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+    </row>
+    <row r="23" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="28"/>
       <c r="L23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="35" t="s">
+      <c r="M23" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-    </row>
-    <row r="25" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="17" t="s">
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+    </row>
+    <row r="25" spans="3:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" s="17" t="s">
+      <c r="D25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="H25" s="17" t="s">
+      <c r="G25" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L25" s="6" t="s">
@@ -2076,30 +2079,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="17">
-        <v>4</v>
-      </c>
-      <c r="E26" s="17">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="17">
-        <v>35</v>
+    <row r="26" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="15">
+        <v>6</v>
+      </c>
+      <c r="E26" s="15">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="15">
+        <v>50</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>48</v>
@@ -2126,59 +2129,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="17" t="s">
+    <row r="27" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="27"/>
+      <c r="D27" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25"/>
       <c r="L27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="35" t="s">
+      <c r="M27" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-    </row>
-    <row r="28" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="17" t="s">
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+    </row>
+    <row r="28" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="27"/>
+      <c r="D28" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="25"/>
       <c r="L28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-    </row>
-    <row r="30" spans="3:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+    </row>
+    <row r="30" spans="3:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="20" t="s">
         <v>0</v>
       </c>
@@ -2228,7 +2231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="20" t="s">
         <v>133</v>
       </c>
@@ -2278,81 +2281,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
       <c r="L32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="29" t="s">
+      <c r="M32" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="31"/>
-    </row>
-    <row r="33" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="32"/>
+    </row>
+    <row r="33" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="27"/>
+      <c r="D33" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
       <c r="L33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="29" t="s">
+      <c r="M33" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="31"/>
-    </row>
-    <row r="35" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="32"/>
+    </row>
+    <row r="35" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="17" t="s">
+      <c r="D35" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="G35" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="J35" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L35" s="11" t="s">
@@ -2380,30 +2383,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="17">
-        <v>3</v>
-      </c>
-      <c r="E36" s="17">
-        <v>1</v>
-      </c>
-      <c r="F36" s="17" t="s">
+    <row r="36" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="15">
+        <v>3</v>
+      </c>
+      <c r="E36" s="15">
+        <v>1</v>
+      </c>
+      <c r="F36" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="17">
-        <v>40</v>
+      <c r="H36" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="15">
+        <v>50</v>
       </c>
       <c r="L36" s="11" t="s">
         <v>51</v>
@@ -2430,59 +2433,59 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="17" t="s">
+    <row r="37" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="27"/>
+      <c r="D37" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
       <c r="L37" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="29" t="s">
+      <c r="M37" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="31"/>
-    </row>
-    <row r="38" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="17" t="s">
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="32"/>
+    </row>
+    <row r="38" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="27"/>
+      <c r="D38" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="25"/>
       <c r="L38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="32"/>
-    </row>
-    <row r="40" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="N38" s="37"/>
+      <c r="O38" s="37"/>
+      <c r="P38" s="37"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+    </row>
+    <row r="40" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="15" t="s">
         <v>0</v>
       </c>
@@ -2532,7 +2535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="15" t="s">
         <v>75</v>
       </c>
@@ -2582,59 +2585,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="25"/>
       <c r="L42" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="29" t="s">
+      <c r="M42" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="31"/>
-    </row>
-    <row r="43" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="32"/>
+    </row>
+    <row r="43" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="25"/>
       <c r="L43" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="29" t="s">
+      <c r="M43" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="31"/>
-    </row>
-    <row r="45" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="32"/>
+    </row>
+    <row r="45" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="20" t="s">
         <v>0</v>
       </c>
@@ -2684,7 +2687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="20" t="s">
         <v>78</v>
       </c>
@@ -2734,81 +2737,81 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="28"/>
       <c r="L47" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="29" t="s">
+      <c r="M47" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
-      <c r="S47" s="31"/>
-    </row>
-    <row r="48" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="32"/>
+    </row>
+    <row r="48" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="28"/>
       <c r="L48" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="29" t="s">
+      <c r="M48" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="S48" s="31"/>
-    </row>
-    <row r="50" spans="3:19" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="20" t="s">
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="32"/>
+    </row>
+    <row r="50" spans="3:19" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D50" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="20" t="s">
+      <c r="D50" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="H50" s="20" t="s">
+      <c r="G50" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I50" s="20" t="s">
+      <c r="I50" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J50" s="20" t="s">
+      <c r="J50" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L50" s="11" t="s">
@@ -2836,30 +2839,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" s="20">
-        <v>2</v>
-      </c>
-      <c r="E51" s="20">
-        <v>1</v>
-      </c>
-      <c r="F51" s="20" t="s">
+    <row r="51" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="15">
+        <v>3</v>
+      </c>
+      <c r="E51" s="15">
+        <v>1</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G51" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="I51" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="J51" s="20">
-        <v>20</v>
+      <c r="H51" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="15">
+        <v>35</v>
       </c>
       <c r="L51" s="11" t="s">
         <v>60</v>
@@ -2886,81 +2889,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="20" t="s">
+    <row r="52" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D52" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="27"/>
+      <c r="D52" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="25"/>
       <c r="L52" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="28" t="s">
+      <c r="M52" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-    </row>
-    <row r="53" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="20" t="s">
+      <c r="N52" s="37"/>
+      <c r="O52" s="37"/>
+      <c r="P52" s="37"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="37"/>
+      <c r="S52" s="37"/>
+    </row>
+    <row r="53" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="27"/>
+      <c r="D53" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="25"/>
       <c r="L53" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M53" s="28" t="s">
+      <c r="M53" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="28"/>
-      <c r="S53" s="28"/>
-    </row>
-    <row r="55" spans="3:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="C55" s="20" t="s">
+      <c r="N53" s="37"/>
+      <c r="O53" s="37"/>
+      <c r="P53" s="37"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="37"/>
+      <c r="S53" s="37"/>
+    </row>
+    <row r="55" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C55" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="20" t="s">
+      <c r="D55" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="H55" s="20" t="s">
+      <c r="G55" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H55" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I55" s="20" t="s">
+      <c r="I55" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J55" s="20" t="s">
+      <c r="J55" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L55" s="19" t="s">
@@ -2988,30 +2991,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C56" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D56" s="20">
-        <v>1</v>
-      </c>
-      <c r="E56" s="20">
-        <v>0</v>
-      </c>
-      <c r="F56" s="20" t="s">
+    <row r="56" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C56" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" s="15">
+        <v>3</v>
+      </c>
+      <c r="E56" s="15">
+        <v>2</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="20" t="s">
+      <c r="G56" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H56" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I56" s="20" t="s">
+      <c r="H56" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I56" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="J56" s="20">
-        <v>20</v>
+      <c r="J56" s="15">
+        <v>30</v>
       </c>
       <c r="L56" s="19" t="s">
         <v>40</v>
@@ -3038,81 +3041,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="20" t="s">
+    <row r="57" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="27"/>
+      <c r="D57" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="25"/>
       <c r="L57" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="29" t="s">
+      <c r="M57" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="N57" s="30"/>
-      <c r="O57" s="30"/>
-      <c r="P57" s="30"/>
-      <c r="Q57" s="30"/>
-      <c r="R57" s="30"/>
-      <c r="S57" s="31"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C58" s="20" t="s">
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="32"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="C58" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="27"/>
+      <c r="D58" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="25"/>
       <c r="L58" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="29" t="s">
+      <c r="M58" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="31"/>
-    </row>
-    <row r="60" spans="3:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="C60" s="20" t="s">
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="32"/>
+    </row>
+    <row r="60" spans="3:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C60" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D60" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F60" s="20" t="s">
+      <c r="D60" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="20" t="s">
+      <c r="G60" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="20" t="s">
+      <c r="I60" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J60" s="20" t="s">
+      <c r="J60" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L60" s="19" t="s">
@@ -3140,30 +3143,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="3:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="C61" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="20">
-        <v>4</v>
-      </c>
-      <c r="E61" s="20">
-        <v>1</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G61" s="20" t="s">
+    <row r="61" spans="3:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C61" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="15">
+        <v>3</v>
+      </c>
+      <c r="E61" s="15">
+        <v>1</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H61" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="I61" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="J61" s="20">
-        <v>60</v>
+      <c r="H61" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" s="15">
+        <v>30</v>
       </c>
       <c r="L61" s="19" t="s">
         <v>62</v>
@@ -3190,59 +3193,59 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="20" t="s">
+    <row r="62" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D62" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="27"/>
+      <c r="D62" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="25"/>
       <c r="L62" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="28" t="s">
+      <c r="M62" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="N62" s="28"/>
-      <c r="O62" s="28"/>
-      <c r="P62" s="28"/>
-      <c r="Q62" s="28"/>
-      <c r="R62" s="28"/>
-      <c r="S62" s="28"/>
-    </row>
-    <row r="63" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="20" t="s">
+      <c r="N62" s="37"/>
+      <c r="O62" s="37"/>
+      <c r="P62" s="37"/>
+      <c r="Q62" s="37"/>
+      <c r="R62" s="37"/>
+      <c r="S62" s="37"/>
+    </row>
+    <row r="63" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="27"/>
+      <c r="D63" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="25"/>
       <c r="L63" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="M63" s="28" t="s">
+      <c r="M63" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="N63" s="28"/>
-      <c r="O63" s="28"/>
-      <c r="P63" s="28"/>
-      <c r="Q63" s="28"/>
-      <c r="R63" s="28"/>
-      <c r="S63" s="28"/>
-    </row>
-    <row r="65" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N63" s="37"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+      <c r="Q63" s="37"/>
+      <c r="R63" s="37"/>
+      <c r="S63" s="37"/>
+    </row>
+    <row r="65" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="15" t="s">
         <v>0</v>
       </c>
@@ -3292,18 +3295,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="15" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="D66" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G66" s="15" t="s">
         <v>7</v>
@@ -3312,7 +3315,7 @@
         <v>8</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="J66" s="15">
         <v>40</v>
@@ -3333,7 +3336,7 @@
         <v>7</v>
       </c>
       <c r="Q66" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R66" s="21" t="s">
         <v>8</v>
@@ -3342,81 +3345,81 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="24"/>
+      <c r="D67" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="25"/>
       <c r="L67" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="29" t="s">
+      <c r="M67" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="31"/>
-    </row>
-    <row r="68" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="32"/>
+    </row>
+    <row r="68" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="24"/>
+      <c r="D68" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="25"/>
       <c r="L68" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M68" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="N68" s="30"/>
-      <c r="O68" s="30"/>
-      <c r="P68" s="30"/>
-      <c r="Q68" s="30"/>
-      <c r="R68" s="30"/>
-      <c r="S68" s="31"/>
-    </row>
-    <row r="70" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="17" t="s">
+      <c r="M68" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
+      <c r="P68" s="31"/>
+      <c r="Q68" s="31"/>
+      <c r="R68" s="31"/>
+      <c r="S68" s="32"/>
+    </row>
+    <row r="70" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D70" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F70" s="17" t="s">
+      <c r="D70" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="H70" s="17" t="s">
+      <c r="G70" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H70" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I70" s="17" t="s">
+      <c r="I70" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="J70" s="17" t="s">
+      <c r="J70" s="15" t="s">
         <v>19</v>
       </c>
       <c r="L70" s="21" t="s">
@@ -3444,30 +3447,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D71" s="17">
-        <v>6</v>
-      </c>
-      <c r="E71" s="17">
-        <v>1</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="17" t="s">
+    <row r="71" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D71" s="15">
+        <v>3</v>
+      </c>
+      <c r="E71" s="15">
+        <v>1</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="15">
         <v>30</v>
-      </c>
-      <c r="H71" s="17">
-        <v>0</v>
-      </c>
-      <c r="I71" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="J71" s="17">
-        <v>50</v>
       </c>
       <c r="L71" s="21" t="s">
         <v>42</v>
@@ -3485,7 +3488,7 @@
         <v>7</v>
       </c>
       <c r="Q71" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R71" s="21" t="s">
         <v>8</v>
@@ -3494,59 +3497,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C72" s="17" t="s">
+    <row r="72" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="27"/>
+      <c r="D72" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24"/>
+      <c r="I72" s="24"/>
+      <c r="J72" s="25"/>
       <c r="L72" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="29" t="s">
+      <c r="M72" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="N72" s="30"/>
-      <c r="O72" s="30"/>
-      <c r="P72" s="30"/>
-      <c r="Q72" s="30"/>
-      <c r="R72" s="30"/>
-      <c r="S72" s="31"/>
-    </row>
-    <row r="73" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C73" s="17" t="s">
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="32"/>
+    </row>
+    <row r="73" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="27"/>
+      <c r="D73" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="25"/>
       <c r="L73" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M73" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="N73" s="28"/>
-      <c r="O73" s="28"/>
-      <c r="P73" s="28"/>
-      <c r="Q73" s="28"/>
-      <c r="R73" s="28"/>
-      <c r="S73" s="28"/>
-    </row>
-    <row r="75" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="N73" s="37"/>
+      <c r="O73" s="37"/>
+      <c r="P73" s="37"/>
+      <c r="Q73" s="37"/>
+      <c r="R73" s="37"/>
+      <c r="S73" s="37"/>
+    </row>
+    <row r="75" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="15" t="s">
         <v>0</v>
       </c>
@@ -3571,146 +3574,441 @@
       <c r="J75" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="76" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L75" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M75" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N75" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O75" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P75" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q75" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R75" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S75" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="15" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D76" s="15">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E76" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="15">
+        <v>40</v>
+      </c>
+      <c r="L76" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="M76" s="22">
+        <v>4</v>
+      </c>
+      <c r="N76" s="22">
+        <v>1</v>
+      </c>
+      <c r="O76" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" s="15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P76" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q76" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="R76" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="S76" s="22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="24"/>
-    </row>
-    <row r="78" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D77" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="25"/>
+      <c r="L77" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M77" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N77" s="31"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="31"/>
+      <c r="S77" s="32"/>
+    </row>
+    <row r="78" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C78" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24"/>
+      <c r="J78" s="25"/>
+      <c r="L78" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M78" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="N78" s="31"/>
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
+      <c r="R78" s="31"/>
+      <c r="S78" s="32"/>
+    </row>
+    <row r="80" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L80" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M80" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N80" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O80" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P80" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R80" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S80" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D81" s="17">
+        <v>6</v>
+      </c>
+      <c r="E81" s="17">
+        <v>1</v>
+      </c>
+      <c r="F81" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H81" s="17">
+        <v>0</v>
+      </c>
+      <c r="I81" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="J81" s="17">
+        <v>50</v>
+      </c>
+      <c r="L81" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="M81" s="22">
+        <v>2</v>
+      </c>
+      <c r="N81" s="22">
+        <v>1</v>
+      </c>
+      <c r="O81" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q81" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="S81" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="28"/>
+      <c r="L82" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M82" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="N82" s="31"/>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
+      <c r="R82" s="31"/>
+      <c r="S82" s="32"/>
+    </row>
+    <row r="83" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="28"/>
+      <c r="L83" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M83" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
+      <c r="R83" s="31"/>
+      <c r="S83" s="32"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="O84"/>
+    </row>
+    <row r="85" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M85" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N85" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O85" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P85" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q85" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R85" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S85" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D86" s="15">
+        <v>12</v>
+      </c>
+      <c r="E86" s="15">
+        <v>3</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I86" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" s="15">
+        <v>100</v>
+      </c>
+      <c r="L86" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="M86" s="22">
+        <v>1</v>
+      </c>
+      <c r="N86" s="22">
+        <v>0</v>
+      </c>
+      <c r="O86" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P86" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q86" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R86" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="S86" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="24"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="24"/>
+      <c r="J87" s="25"/>
+      <c r="L87" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M87" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="N87" s="31"/>
+      <c r="O87" s="31"/>
+      <c r="P87" s="31"/>
+      <c r="Q87" s="31"/>
+      <c r="R87" s="31"/>
+      <c r="S87" s="32"/>
+    </row>
+    <row r="88" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="24"/>
-    </row>
-    <row r="80" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I80" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D81" s="15">
-        <v>1</v>
-      </c>
-      <c r="E81" s="15">
-        <v>2</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G81" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="23"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="24"/>
-    </row>
-    <row r="83" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="15" t="s">
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="24"/>
+      <c r="J88" s="25"/>
+      <c r="L88" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="23"/>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="24"/>
-    </row>
-    <row r="85" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="N88" s="31"/>
+      <c r="O88" s="31"/>
+      <c r="P88" s="31"/>
+      <c r="Q88" s="31"/>
+      <c r="R88" s="31"/>
+      <c r="S88" s="32"/>
+    </row>
+    <row r="90" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="15" t="s">
         <v>0</v>
       </c>
@@ -3735,62 +4033,134 @@
       <c r="J90" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="91" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L90" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M90" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N90" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O90" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P90" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q90" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R90" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S90" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="15" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D91" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>7</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>8</v>
       </c>
       <c r="J91" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="L91" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M91" s="22">
+        <v>5</v>
+      </c>
+      <c r="N91" s="22">
+        <v>2</v>
+      </c>
+      <c r="O91" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P91" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q91" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="22">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D92" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="24"/>
-    </row>
-    <row r="93" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D92" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="24"/>
+      <c r="J92" s="25"/>
+      <c r="L92" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M92" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="N92" s="31"/>
+      <c r="O92" s="31"/>
+      <c r="P92" s="31"/>
+      <c r="Q92" s="31"/>
+      <c r="R92" s="31"/>
+      <c r="S92" s="32"/>
+    </row>
+    <row r="93" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="24"/>
-    </row>
-    <row r="95" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D93" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+      <c r="I93" s="24"/>
+      <c r="J93" s="25"/>
+      <c r="L93" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M93" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="N93" s="31"/>
+      <c r="O93" s="31"/>
+      <c r="P93" s="31"/>
+      <c r="Q93" s="31"/>
+      <c r="R93" s="31"/>
+      <c r="S93" s="32"/>
+    </row>
+    <row r="95" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="15" t="s">
         <v>0</v>
       </c>
@@ -3815,8 +4185,32 @@
       <c r="J95" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="96" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L95" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M95" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N95" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O95" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P95" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q95" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R95" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S95" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="15" t="s">
         <v>108</v>
       </c>
@@ -3841,36 +4235,87 @@
       <c r="J96" s="15">
         <v>50</v>
       </c>
-    </row>
-    <row r="97" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L96" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="M96" s="22">
+        <v>3</v>
+      </c>
+      <c r="N96" s="22">
+        <v>1</v>
+      </c>
+      <c r="O96" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="P96" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q96" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="S96" s="22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="22" t="s">
+      <c r="D97" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="23"/>
-      <c r="H97" s="23"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="24"/>
-    </row>
-    <row r="98" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="25"/>
+      <c r="L97" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M97" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="N97" s="31"/>
+      <c r="O97" s="31"/>
+      <c r="P97" s="31"/>
+      <c r="Q97" s="31"/>
+      <c r="R97" s="31"/>
+      <c r="S97" s="32"/>
+    </row>
+    <row r="98" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D98" s="22" t="s">
+      <c r="D98" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E98" s="23"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
-      <c r="H98" s="23"/>
-      <c r="I98" s="23"/>
-      <c r="J98" s="24"/>
-    </row>
-    <row r="100" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+      <c r="I98" s="24"/>
+      <c r="J98" s="25"/>
+      <c r="L98" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M98" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="N98" s="31"/>
+      <c r="O98" s="31"/>
+      <c r="P98" s="31"/>
+      <c r="Q98" s="31"/>
+      <c r="R98" s="31"/>
+      <c r="S98" s="32"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="O99"/>
+    </row>
+    <row r="100" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="15" t="s">
         <v>0</v>
       </c>
@@ -3895,8 +4340,32 @@
       <c r="J100" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="101" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L100" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M100" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N100" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="O100" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P100" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="15" t="s">
         <v>112</v>
       </c>
@@ -3921,36 +4390,87 @@
       <c r="J101" s="15">
         <v>50</v>
       </c>
-    </row>
-    <row r="102" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L101" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="M101" s="22">
+        <v>3</v>
+      </c>
+      <c r="N101" s="22">
+        <v>1</v>
+      </c>
+      <c r="O101" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P101" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q101" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D102" s="22" t="s">
+      <c r="D102" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="E102" s="23"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="23"/>
-      <c r="H102" s="23"/>
-      <c r="I102" s="23"/>
-      <c r="J102" s="24"/>
-    </row>
-    <row r="103" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
+      <c r="J102" s="25"/>
+      <c r="L102" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M102" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="N102" s="31"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
+      <c r="S102" s="32"/>
+    </row>
+    <row r="103" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D103" s="22" t="s">
+      <c r="D103" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
-      <c r="H103" s="23"/>
-      <c r="I103" s="23"/>
-      <c r="J103" s="24"/>
-    </row>
-    <row r="105" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
+      <c r="J103" s="25"/>
+      <c r="L103" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M103" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="N103" s="31"/>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
+      <c r="R103" s="31"/>
+      <c r="S103" s="32"/>
+    </row>
+    <row r="104" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="O104"/>
+    </row>
+    <row r="105" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="15" t="s">
         <v>0</v>
       </c>
@@ -3976,7 +4496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="15" t="s">
         <v>119</v>
       </c>
@@ -4002,35 +4522,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="22" t="s">
+      <c r="D107" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="23"/>
-      <c r="J107" s="24"/>
-    </row>
-    <row r="108" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="25"/>
+    </row>
+    <row r="108" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="22" t="s">
+      <c r="D108" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="23"/>
-      <c r="H108" s="23"/>
-      <c r="I108" s="23"/>
-      <c r="J108" s="24"/>
-    </row>
-    <row r="110" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="25"/>
+    </row>
+    <row r="110" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="15" t="s">
         <v>0</v>
       </c>
@@ -4056,7 +4576,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="15" t="s">
         <v>121</v>
       </c>
@@ -4082,35 +4602,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D112" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
-      <c r="G112" s="23"/>
-      <c r="H112" s="23"/>
-      <c r="I112" s="23"/>
-      <c r="J112" s="24"/>
-    </row>
-    <row r="113" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="25"/>
+    </row>
+    <row r="113" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D113" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="E113" s="23"/>
-      <c r="F113" s="23"/>
-      <c r="G113" s="23"/>
-      <c r="H113" s="23"/>
-      <c r="I113" s="23"/>
-      <c r="J113" s="24"/>
-    </row>
-    <row r="115" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="25"/>
+    </row>
+    <row r="115" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="15" t="s">
         <v>0</v>
       </c>
@@ -4136,7 +4656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="15" t="s">
         <v>124</v>
       </c>
@@ -4162,35 +4682,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="22" t="s">
+      <c r="D117" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="E117" s="23"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
-      <c r="J117" s="24"/>
-    </row>
-    <row r="118" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="25"/>
+    </row>
+    <row r="118" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="D118" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="E118" s="23"/>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
-      <c r="H118" s="23"/>
-      <c r="I118" s="23"/>
-      <c r="J118" s="24"/>
-    </row>
-    <row r="120" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="25"/>
+    </row>
+    <row r="120" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="15" t="s">
         <v>0</v>
       </c>
@@ -4216,7 +4736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="12" t="s">
         <v>127</v>
       </c>
@@ -4242,35 +4762,35 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="3:10" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D122" s="22" t="s">
+      <c r="D122" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="23"/>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-      <c r="J122" s="24"/>
-    </row>
-    <row r="123" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="24"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="24"/>
+      <c r="H122" s="24"/>
+      <c r="I122" s="24"/>
+      <c r="J122" s="25"/>
+    </row>
+    <row r="123" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D123" s="22" t="s">
+      <c r="D123" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="24"/>
-    </row>
-    <row r="125" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="25"/>
+    </row>
+    <row r="125" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="15" t="s">
         <v>0</v>
       </c>
@@ -4296,7 +4816,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C126" s="15" t="s">
         <v>132</v>
       </c>
@@ -4322,39 +4842,115 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="3:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C127" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D127" s="22" t="s">
+      <c r="D127" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="E127" s="23"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
-      <c r="I127" s="23"/>
-      <c r="J127" s="24"/>
-    </row>
-    <row r="128" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="25"/>
+    </row>
+    <row r="128" spans="3:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D128" s="22" t="s">
+      <c r="D128" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="23"/>
-      <c r="I128" s="23"/>
-      <c r="J128" s="24"/>
-    </row>
-    <row r="130" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="25"/>
+    </row>
+    <row r="130" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F130" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J130" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C131" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D131" s="15">
+        <v>3</v>
+      </c>
+      <c r="E131" s="15">
+        <v>1</v>
+      </c>
+      <c r="F131" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="H131" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I131" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J131" s="15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="132" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C132" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="25"/>
+    </row>
+    <row r="133" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C133" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E133" s="24"/>
+      <c r="F133" s="24"/>
+      <c r="G133" s="24"/>
+      <c r="H133" s="24"/>
+      <c r="I133" s="24"/>
+      <c r="J133" s="25"/>
+    </row>
+    <row r="134" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C134" s="18"/>
       <c r="D134" s="18"/>
       <c r="E134" s="18"/>
@@ -4369,7 +4965,7 @@
       <c r="P134"/>
       <c r="Q134"/>
     </row>
-    <row r="135" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="15" t="s">
         <v>0</v>
       </c>
@@ -4400,18 +4996,18 @@
       <c r="P135"/>
       <c r="Q135"/>
     </row>
-    <row r="136" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D136" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E136" s="15">
         <v>1</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G136" s="15" t="s">
         <v>7</v>
@@ -4420,10 +5016,10 @@
         <v>8</v>
       </c>
       <c r="I136" s="15" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="J136" s="15">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M136"/>
       <c r="N136"/>
@@ -4431,45 +5027,45 @@
       <c r="P136"/>
       <c r="Q136"/>
     </row>
-    <row r="137" spans="3:17" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:17" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D137" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E137" s="23"/>
-      <c r="F137" s="23"/>
-      <c r="G137" s="23"/>
-      <c r="H137" s="23"/>
-      <c r="I137" s="23"/>
-      <c r="J137" s="24"/>
+      <c r="D137" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E137" s="24"/>
+      <c r="F137" s="24"/>
+      <c r="G137" s="24"/>
+      <c r="H137" s="24"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="25"/>
       <c r="M137"/>
       <c r="N137"/>
       <c r="O137"/>
       <c r="P137"/>
       <c r="Q137"/>
     </row>
-    <row r="138" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D138" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="23"/>
-      <c r="I138" s="23"/>
-      <c r="J138" s="24"/>
+      <c r="D138" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="25"/>
       <c r="M138"/>
       <c r="N138"/>
       <c r="O138"/>
       <c r="P138"/>
       <c r="Q138"/>
     </row>
-    <row r="139" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="18"/>
       <c r="D139" s="18"/>
       <c r="E139" s="18"/>
@@ -4484,436 +5080,33 @@
       <c r="P139"/>
       <c r="Q139"/>
     </row>
-    <row r="140" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C140" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E140" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F140" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H140" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I140" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J140" s="15" t="s">
-        <v>19</v>
-      </c>
+    <row r="140" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M140"/>
       <c r="N140"/>
       <c r="O140"/>
       <c r="P140"/>
       <c r="Q140"/>
     </row>
-    <row r="141" spans="3:17" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C141" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D141" s="15">
-        <v>4</v>
-      </c>
-      <c r="E141" s="15">
-        <v>1</v>
-      </c>
-      <c r="F141" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G141" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H141" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I141" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="J141" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="142" spans="3:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C142" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D142" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E142" s="23"/>
-      <c r="F142" s="23"/>
-      <c r="G142" s="23"/>
-      <c r="H142" s="23"/>
-      <c r="I142" s="23"/>
-      <c r="J142" s="24"/>
-    </row>
-    <row r="143" spans="3:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C143" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D143" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E143" s="23"/>
-      <c r="F143" s="23"/>
-      <c r="G143" s="23"/>
-      <c r="H143" s="23"/>
-      <c r="I143" s="23"/>
-      <c r="J143" s="24"/>
-    </row>
-    <row r="145" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D145" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E145" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F145" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G145" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H145" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I145" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J145" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="146" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D146" s="15">
-        <v>4</v>
-      </c>
-      <c r="E146" s="15">
-        <v>1</v>
-      </c>
-      <c r="F146" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G146" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H146" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I146" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J146" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="147" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D147" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E147" s="23"/>
-      <c r="F147" s="23"/>
-      <c r="G147" s="23"/>
-      <c r="H147" s="23"/>
-      <c r="I147" s="23"/>
-      <c r="J147" s="24"/>
-    </row>
-    <row r="148" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="E148" s="23"/>
-      <c r="F148" s="23"/>
-      <c r="G148" s="23"/>
-      <c r="H148" s="23"/>
-      <c r="I148" s="23"/>
-      <c r="J148" s="24"/>
-    </row>
-    <row r="150" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C150" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E150" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F150" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H150" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I150" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J150" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="151" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D151" s="15">
-        <v>6</v>
-      </c>
-      <c r="E151" s="15">
-        <v>1</v>
-      </c>
-      <c r="F151" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G151" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H151" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="I151" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J151" s="15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="152" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D152" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E152" s="23"/>
-      <c r="F152" s="23"/>
-      <c r="G152" s="23"/>
-      <c r="H152" s="23"/>
-      <c r="I152" s="23"/>
-      <c r="J152" s="24"/>
-    </row>
-    <row r="153" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="E153" s="23"/>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
-      <c r="H153" s="23"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="24"/>
-    </row>
-    <row r="155" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E155" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F155" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H155" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I155" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J155" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="156" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C156" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D156" s="15">
-        <v>3</v>
-      </c>
-      <c r="E156" s="15">
-        <v>1</v>
-      </c>
-      <c r="F156" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G156" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H156" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I156" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J156" s="15">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="157" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C157" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D157" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E157" s="23"/>
-      <c r="F157" s="23"/>
-      <c r="G157" s="23"/>
-      <c r="H157" s="23"/>
-      <c r="I157" s="23"/>
-      <c r="J157" s="24"/>
-    </row>
-    <row r="158" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C158" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="E158" s="23"/>
-      <c r="F158" s="23"/>
-      <c r="G158" s="23"/>
-      <c r="H158" s="23"/>
-      <c r="I158" s="23"/>
-      <c r="J158" s="24"/>
-    </row>
-    <row r="160" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C160" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D160" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E160" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F160" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G160" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H160" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I160" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J160" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C161" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D161" s="15">
-        <v>3</v>
-      </c>
-      <c r="E161" s="15">
-        <v>2</v>
-      </c>
-      <c r="F161" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G161" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H161" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I161" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J161" s="15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="162" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C162" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E162" s="23"/>
-      <c r="F162" s="23"/>
-      <c r="G162" s="23"/>
-      <c r="H162" s="23"/>
-      <c r="I162" s="23"/>
-      <c r="J162" s="24"/>
-    </row>
-    <row r="163" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C163" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E163" s="23"/>
-      <c r="F163" s="23"/>
-      <c r="G163" s="23"/>
-      <c r="H163" s="23"/>
-      <c r="I163" s="23"/>
-      <c r="J163" s="24"/>
-    </row>
-    <row r="165" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C165" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D165" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E165" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F165" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G165" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H165" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I165" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J165" s="15" t="s">
-        <v>19</v>
-      </c>
+    <row r="141" spans="3:17" ht="47.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" spans="3:17" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" spans="3:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L165"/>
       <c r="M165"/>
       <c r="N165"/>
@@ -4923,31 +5116,7 @@
       <c r="R165"/>
       <c r="S165"/>
     </row>
-    <row r="166" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C166" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D166" s="15">
-        <v>3</v>
-      </c>
-      <c r="E166" s="15">
-        <v>1</v>
-      </c>
-      <c r="F166" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G166" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I166" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J166" s="15">
-        <v>30</v>
-      </c>
+    <row r="166" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L166"/>
       <c r="M166"/>
       <c r="N166"/>
@@ -4957,291 +5126,44 @@
       <c r="R166"/>
       <c r="S166"/>
     </row>
-    <row r="167" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C167" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="E167" s="23"/>
-      <c r="F167" s="23"/>
-      <c r="G167" s="23"/>
-      <c r="H167" s="23"/>
-      <c r="I167" s="23"/>
-      <c r="J167" s="24"/>
+    <row r="167" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L167"/>
-      <c r="M167" s="36"/>
-      <c r="N167" s="36"/>
-      <c r="O167" s="36"/>
-      <c r="P167" s="36"/>
-      <c r="Q167" s="36"/>
-      <c r="R167" s="36"/>
-      <c r="S167" s="36"/>
-    </row>
-    <row r="168" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C168" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="E168" s="23"/>
-      <c r="F168" s="23"/>
-      <c r="G168" s="23"/>
-      <c r="H168" s="23"/>
-      <c r="I168" s="23"/>
-      <c r="J168" s="24"/>
+      <c r="M167" s="33"/>
+      <c r="N167" s="33"/>
+      <c r="O167" s="33"/>
+      <c r="P167" s="33"/>
+      <c r="Q167" s="33"/>
+      <c r="R167" s="33"/>
+      <c r="S167" s="33"/>
+    </row>
+    <row r="168" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L168"/>
-      <c r="M168" s="36"/>
-      <c r="N168" s="36"/>
-      <c r="O168" s="36"/>
-      <c r="P168" s="36"/>
-      <c r="Q168" s="36"/>
-      <c r="R168" s="36"/>
-      <c r="S168" s="36"/>
-    </row>
-    <row r="170" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C170" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E170" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F170" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G170" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H170" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I170" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J170" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="171" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C171" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D171" s="15">
-        <v>4</v>
-      </c>
-      <c r="E171" s="15">
-        <v>2</v>
-      </c>
-      <c r="F171" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H171" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I171" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J171" s="15">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="172" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C172" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D172" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="E172" s="23"/>
-      <c r="F172" s="23"/>
-      <c r="G172" s="23"/>
-      <c r="H172" s="23"/>
-      <c r="I172" s="23"/>
-      <c r="J172" s="24"/>
-    </row>
-    <row r="173" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C173" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D173" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="E173" s="23"/>
-      <c r="F173" s="23"/>
-      <c r="G173" s="23"/>
-      <c r="H173" s="23"/>
-      <c r="I173" s="23"/>
-      <c r="J173" s="24"/>
-    </row>
-    <row r="175" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C175" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E175" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F175" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G175" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="H175" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="I175" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J175" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="176" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C176" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D176" s="15">
-        <v>3</v>
-      </c>
-      <c r="E176" s="15">
-        <v>1</v>
-      </c>
-      <c r="F176" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G176" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H176" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I176" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J176" s="15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="177" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C177" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D177" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="E177" s="23"/>
-      <c r="F177" s="23"/>
-      <c r="G177" s="23"/>
-      <c r="H177" s="23"/>
-      <c r="I177" s="23"/>
-      <c r="J177" s="24"/>
-    </row>
-    <row r="178" spans="3:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C178" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D178" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E178" s="23"/>
-      <c r="F178" s="23"/>
-      <c r="G178" s="23"/>
-      <c r="H178" s="23"/>
-      <c r="I178" s="23"/>
-      <c r="J178" s="24"/>
-    </row>
+      <c r="M168" s="33"/>
+      <c r="N168" s="33"/>
+      <c r="O168" s="33"/>
+      <c r="P168" s="33"/>
+      <c r="Q168" s="33"/>
+      <c r="R168" s="33"/>
+      <c r="S168" s="33"/>
+    </row>
+    <row r="170" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="12:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="D127:J127"/>
-    <mergeCell ref="D128:J128"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D137:J137"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="M67:S67"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="M167:S167"/>
-    <mergeCell ref="M168:S168"/>
-    <mergeCell ref="D168:J168"/>
-    <mergeCell ref="D172:J172"/>
-    <mergeCell ref="D173:J173"/>
-    <mergeCell ref="D138:J138"/>
-    <mergeCell ref="D142:J142"/>
-    <mergeCell ref="D143:J143"/>
-    <mergeCell ref="D147:J147"/>
-    <mergeCell ref="D148:J148"/>
-    <mergeCell ref="D177:J177"/>
-    <mergeCell ref="D178:J178"/>
-    <mergeCell ref="D157:J157"/>
-    <mergeCell ref="D158:J158"/>
-    <mergeCell ref="D162:J162"/>
-    <mergeCell ref="D163:J163"/>
-    <mergeCell ref="D167:J167"/>
-    <mergeCell ref="D152:J152"/>
-    <mergeCell ref="D153:J153"/>
-    <mergeCell ref="V17:AB17"/>
-    <mergeCell ref="V18:AB18"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="M32:S32"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="M28:S28"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="V12:AB12"/>
-    <mergeCell ref="V13:AB13"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="V8:AB8"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="M72:S72"/>
-    <mergeCell ref="M73:S73"/>
     <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="M53:S53"/>
-    <mergeCell ref="M62:S62"/>
-    <mergeCell ref="M68:S68"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="M63:S63"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D43:J43"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="M42:S42"/>
-    <mergeCell ref="M43:S43"/>
-    <mergeCell ref="M47:S47"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M52:S52"/>
-    <mergeCell ref="D57:J57"/>
-    <mergeCell ref="D58:J58"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="D63:J63"/>
+    <mergeCell ref="D97:J97"/>
+    <mergeCell ref="D98:J98"/>
+    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="M87:S87"/>
+    <mergeCell ref="M88:S88"/>
+    <mergeCell ref="M77:S77"/>
+    <mergeCell ref="M78:S78"/>
     <mergeCell ref="M57:S57"/>
     <mergeCell ref="M58:S58"/>
     <mergeCell ref="D118:J118"/>
@@ -5252,20 +5174,91 @@
     <mergeCell ref="D112:J112"/>
     <mergeCell ref="D113:J113"/>
     <mergeCell ref="D117:J117"/>
+    <mergeCell ref="D77:J77"/>
+    <mergeCell ref="D78:J78"/>
+    <mergeCell ref="D93:J93"/>
+    <mergeCell ref="D82:J82"/>
+    <mergeCell ref="D83:J83"/>
+    <mergeCell ref="D87:J87"/>
+    <mergeCell ref="D88:J88"/>
+    <mergeCell ref="D92:J92"/>
+    <mergeCell ref="D103:J103"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D43:J43"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D48:J48"/>
+    <mergeCell ref="M82:S82"/>
+    <mergeCell ref="M83:S83"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M47:S47"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M52:S52"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="M7:S7"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="V8:AB8"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="M27:S27"/>
+    <mergeCell ref="M28:S28"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="D72:J72"/>
+    <mergeCell ref="D73:J73"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D62:J62"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="M167:S167"/>
+    <mergeCell ref="M168:S168"/>
+    <mergeCell ref="D63:J63"/>
     <mergeCell ref="D67:J67"/>
     <mergeCell ref="D68:J68"/>
-    <mergeCell ref="D83:J83"/>
-    <mergeCell ref="D72:J72"/>
-    <mergeCell ref="D73:J73"/>
-    <mergeCell ref="D77:J77"/>
-    <mergeCell ref="D78:J78"/>
-    <mergeCell ref="D82:J82"/>
-    <mergeCell ref="D103:J103"/>
-    <mergeCell ref="D92:J92"/>
-    <mergeCell ref="D93:J93"/>
-    <mergeCell ref="D97:J97"/>
-    <mergeCell ref="D98:J98"/>
-    <mergeCell ref="D102:J102"/>
+    <mergeCell ref="D133:J133"/>
+    <mergeCell ref="D137:J137"/>
+    <mergeCell ref="D138:J138"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D127:J127"/>
+    <mergeCell ref="D128:J128"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="D132:J132"/>
+    <mergeCell ref="M92:S92"/>
+    <mergeCell ref="M93:S93"/>
+    <mergeCell ref="M22:S22"/>
+    <mergeCell ref="M67:S67"/>
+    <mergeCell ref="M97:S97"/>
+    <mergeCell ref="M72:S72"/>
+    <mergeCell ref="M73:S73"/>
+    <mergeCell ref="M103:S103"/>
+    <mergeCell ref="M98:S98"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="M53:S53"/>
+    <mergeCell ref="M62:S62"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="M102:S102"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="M63:S63"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5275,42 +5268,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
     </row>
   </sheetData>
@@ -5324,7 +5317,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
